--- a/data/links.xlsx
+++ b/data/links.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Crypto\Private\LQDU\LinkBoard\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Crypto\Private\NSFW\LinkBoard\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F60F8677-7D53-4416-9EC4-AC76814393A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4289427-8435-456C-85F6-BBFB3FE61AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15960" tabRatio="394" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2441" uniqueCount="798">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2441" uniqueCount="797">
   <si>
     <t>https://xhamster18.desi/videos/nubile-films-seductive-games-of-passion-3267609</t>
   </si>
@@ -1504,9 +1504,6 @@
   </si>
   <si>
     <t>ashley fires</t>
-  </si>
-  <si>
-    <t>chastity cage normal</t>
   </si>
   <si>
     <t>lolipop plug</t>
@@ -2534,21 +2531,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6161"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6161"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -2912,7 +2895,7 @@
     </row>
     <row r="2" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B2" s="2">
         <v>87</v>
@@ -2921,7 +2904,7 @@
         <v>167</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>43</v>
@@ -2936,7 +2919,7 @@
         <v>292</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>137</v>
@@ -2948,7 +2931,7 @@
         <v>67</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>380</v>
@@ -2966,7 +2949,7 @@
         <v>8</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="T2" s="2" t="str" cm="1">
         <f t="array" ref="T2">_xlfn.REGEXEXTRACT(A2,"(?&lt;=//)[^/]+")</f>
@@ -2975,7 +2958,7 @@
     </row>
     <row r="3" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B3" s="2">
         <v>57</v>
@@ -2984,7 +2967,7 @@
         <v>436</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>43</v>
@@ -3008,10 +2991,10 @@
         <v>82</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>435</v>
@@ -3029,7 +3012,7 @@
         <v>8</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="T3" s="2" t="str" cm="1">
         <f t="array" ref="T3">_xlfn.REGEXEXTRACT(A3,"(?&lt;=//)[^/]+")</f>
@@ -3038,16 +3021,16 @@
     </row>
     <row r="4" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B4" s="2">
         <v>0</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>43</v>
@@ -3068,13 +3051,13 @@
         <v>67</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>82</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>435</v>
@@ -3092,7 +3075,7 @@
         <v>8</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="T4" s="2" t="str" cm="1">
         <f t="array" ref="T4">_xlfn.REGEXEXTRACT(A4,"(?&lt;=//)[^/]+")</f>
@@ -3101,16 +3084,16 @@
     </row>
     <row r="5" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B5" s="2">
         <v>0</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>43</v>
@@ -3122,7 +3105,7 @@
         <v>156</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>343</v>
@@ -3134,16 +3117,16 @@
         <v>157</v>
       </c>
       <c r="L5" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="M5" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="N5" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="O5" s="2" t="s">
         <v>679</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>680</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>152</v>
@@ -3155,7 +3138,7 @@
         <v>8</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="T5" s="2" t="str" cm="1">
         <f t="array" ref="T5">_xlfn.REGEXEXTRACT(A5,"(?&lt;=//)[^/]+")</f>
@@ -3164,16 +3147,16 @@
     </row>
     <row r="6" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B6" s="2">
         <v>111</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>43</v>
@@ -3188,10 +3171,10 @@
         <v>98</v>
       </c>
       <c r="I6" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>596</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>597</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>466</v>
@@ -3203,13 +3186,13 @@
         <v>67</v>
       </c>
       <c r="N6" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="P6" s="2" t="s">
         <v>599</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>600</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>56</v>
@@ -3218,7 +3201,7 @@
         <v>7</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="T6" s="2" t="str" cm="1">
         <f t="array" ref="T6">_xlfn.REGEXEXTRACT(A6,"(?&lt;=//)[^/]+")</f>
@@ -3248,7 +3231,7 @@
         <v>79</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>98</v>
@@ -3290,7 +3273,7 @@
     </row>
     <row r="8" spans="1:20" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B8" s="2">
         <v>73</v>
@@ -3299,7 +3282,7 @@
         <v>273</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>43</v>
@@ -3311,7 +3294,7 @@
         <v>80</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>84</v>
@@ -3323,16 +3306,16 @@
         <v>82</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>332</v>
       </c>
       <c r="N8" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="O8" s="2" t="s">
         <v>592</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>593</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>337</v>
@@ -3344,7 +3327,7 @@
         <v>7</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="T8" s="2" t="str" cm="1">
         <f t="array" ref="T8">_xlfn.REGEXEXTRACT(A8,"(?&lt;=//)[^/]+")</f>
@@ -3353,7 +3336,7 @@
     </row>
     <row r="9" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B9" s="2">
         <v>56</v>
@@ -3362,7 +3345,7 @@
         <v>95</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>43</v>
@@ -3380,7 +3363,7 @@
         <v>98</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>434</v>
@@ -3395,7 +3378,7 @@
         <v>130</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>152</v>
@@ -3407,7 +3390,7 @@
         <v>7</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="T9" s="2" t="str" cm="1">
         <f t="array" ref="T9">_xlfn.REGEXEXTRACT(A9,"(?&lt;=//)[^/]+")</f>
@@ -3668,7 +3651,7 @@
     </row>
     <row r="14" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B14" s="2">
         <v>46</v>
@@ -3677,7 +3660,7 @@
         <v>154</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>43</v>
@@ -3689,7 +3672,7 @@
         <v>156</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>117</v>
@@ -3713,7 +3696,7 @@
         <v>152</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>56</v>
@@ -3722,7 +3705,7 @@
         <v>7</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="T14" s="2" t="str" cm="1">
         <f t="array" ref="T14">_xlfn.REGEXEXTRACT(A14,"(?&lt;=//)[^/]+")</f>
@@ -3731,7 +3714,7 @@
     </row>
     <row r="15" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B15" s="2">
         <v>0</v>
@@ -3740,7 +3723,7 @@
         <v>154</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>43</v>
@@ -3764,7 +3747,7 @@
         <v>292</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>343</v>
@@ -3785,7 +3768,7 @@
         <v>7</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="T15" s="2" t="str" cm="1">
         <f t="array" ref="T15">_xlfn.REGEXEXTRACT(A15,"(?&lt;=//)[^/]+")</f>
@@ -3800,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>250</v>
@@ -3857,7 +3840,7 @@
     </row>
     <row r="17" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B17" s="2">
         <v>0</v>
@@ -3866,7 +3849,7 @@
         <v>154</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>43</v>
@@ -3887,10 +3870,10 @@
         <v>292</v>
       </c>
       <c r="K17" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="L17" s="2" t="s">
         <v>660</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>661</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>466</v>
@@ -3911,7 +3894,7 @@
         <v>7</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="T17" s="2" t="str" cm="1">
         <f t="array" ref="T17">_xlfn.REGEXEXTRACT(A17,"(?&lt;=//)[^/]+")</f>
@@ -3920,16 +3903,16 @@
     </row>
     <row r="18" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B18" s="2">
         <v>0</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>43</v>
@@ -3941,7 +3924,7 @@
         <v>156</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>343</v>
@@ -3953,7 +3936,7 @@
         <v>159</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>233</v>
@@ -3962,7 +3945,7 @@
         <v>91</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="P18" s="2" t="s">
         <v>91</v>
@@ -3974,7 +3957,7 @@
         <v>7</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="T18" s="2" t="str" cm="1">
         <f t="array" ref="T18">_xlfn.REGEXEXTRACT(A18,"(?&lt;=//)[^/]+")</f>
@@ -3983,16 +3966,16 @@
     </row>
     <row r="19" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B19" s="2">
         <v>0</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>43</v>
@@ -4001,7 +3984,7 @@
         <v>43</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>43</v>
@@ -4022,13 +4005,13 @@
         <v>43</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="O19" s="2" t="s">
         <v>358</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="Q19" s="2" t="s">
         <v>56</v>
@@ -4037,7 +4020,7 @@
         <v>7</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="T19" s="2" t="str" cm="1">
         <f t="array" ref="T19">_xlfn.REGEXEXTRACT(A19,"(?&lt;=//)[^/]+")</f>
@@ -4046,16 +4029,16 @@
     </row>
     <row r="20" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B20" s="2">
         <v>0</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>43</v>
@@ -4064,7 +4047,7 @@
         <v>43</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>43</v>
@@ -4085,10 +4068,10 @@
         <v>43</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="P20" s="2" t="s">
         <v>91</v>
@@ -4100,7 +4083,7 @@
         <v>7</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="T20" s="2" t="str" cm="1">
         <f t="array" ref="T20">_xlfn.REGEXEXTRACT(A20,"(?&lt;=//)[^/]+")</f>
@@ -4109,7 +4092,7 @@
     </row>
     <row r="21" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B21" s="2">
         <v>46</v>
@@ -4118,10 +4101,10 @@
         <v>112</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>791</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>792</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>793</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>43</v>
@@ -4136,16 +4119,16 @@
         <v>98</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>93</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>429</v>
@@ -4163,7 +4146,7 @@
         <v>7</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="T21" s="2" t="str" cm="1">
         <f t="array" ref="T21">_xlfn.REGEXEXTRACT(A21,"(?&lt;=//)[^/]+")</f>
@@ -4172,16 +4155,16 @@
     </row>
     <row r="22" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B22" s="2">
         <v>113</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>43</v>
@@ -4193,10 +4176,10 @@
         <v>156</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>340</v>
@@ -4217,16 +4200,16 @@
         <v>91</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="R22" s="2">
         <v>6</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="T22" s="2" t="str" cm="1">
         <f t="array" ref="T22">_xlfn.REGEXEXTRACT(A22,"(?&lt;=//)[^/]+")</f>
@@ -4298,7 +4281,7 @@
     </row>
     <row r="24" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B24" s="2">
         <v>66</v>
@@ -4307,7 +4290,7 @@
         <v>112</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>43</v>
@@ -4352,7 +4335,7 @@
         <v>6</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="T24" s="2" t="str" cm="1">
         <f t="array" ref="T24">_xlfn.REGEXEXTRACT(A24,"(?&lt;=//)[^/]+")</f>
@@ -4361,7 +4344,7 @@
     </row>
     <row r="25" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B25" s="2">
         <v>57</v>
@@ -4370,7 +4353,7 @@
         <v>468</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>43</v>
@@ -4415,7 +4398,7 @@
         <v>6</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="T25" s="2" t="str" cm="1">
         <f t="array" ref="T25">_xlfn.REGEXEXTRACT(A25,"(?&lt;=//)[^/]+")</f>
@@ -4433,7 +4416,7 @@
         <v>95</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>43</v>
@@ -4454,22 +4437,22 @@
         <v>442</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>92</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="Q26" s="2" t="s">
         <v>56</v>
@@ -4478,7 +4461,7 @@
         <v>6</v>
       </c>
       <c r="S26" s="2" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="T26" s="2" t="str" cm="1">
         <f t="array" ref="T26">_xlfn.REGEXEXTRACT(A26,"(?&lt;=//)[^/]+")</f>
@@ -4571,7 +4554,7 @@
         <v>79</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>312</v>
@@ -4793,7 +4776,7 @@
         <v>6</v>
       </c>
       <c r="S31" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T31" s="2" t="str" cm="1">
         <f t="array" ref="T31">_xlfn.REGEXEXTRACT(A31,"(?&lt;=//)[^/]+")</f>
@@ -4835,7 +4818,7 @@
         <v>306</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>435</v>
@@ -4949,7 +4932,7 @@
         <v>321</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>84</v>
@@ -5054,16 +5037,16 @@
     </row>
     <row r="36" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B36" s="2">
         <v>20</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>43</v>
@@ -5075,13 +5058,13 @@
         <v>80</v>
       </c>
       <c r="H36" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="J36" s="2" t="s">
         <v>632</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>633</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>43</v>
@@ -5096,19 +5079,19 @@
         <v>380</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="P36" s="2" t="s">
         <v>91</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="R36" s="2">
         <v>6</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="T36" s="2" t="str" cm="1">
         <f t="array" ref="T36">_xlfn.REGEXEXTRACT(A36,"(?&lt;=//)[^/]+")</f>
@@ -5117,13 +5100,13 @@
     </row>
     <row r="37" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B37" s="2">
         <v>0</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>351</v>
@@ -5138,7 +5121,7 @@
         <v>320</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>84</v>
@@ -5150,10 +5133,10 @@
         <v>228</v>
       </c>
       <c r="L37" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="M37" s="2" t="s">
         <v>540</v>
-      </c>
-      <c r="M37" s="2" t="s">
-        <v>541</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>92</v>
@@ -5171,7 +5154,7 @@
         <v>6</v>
       </c>
       <c r="S37" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="T37" s="2" t="str" cm="1">
         <f t="array" ref="T37">_xlfn.REGEXEXTRACT(A37,"(?&lt;=//)[^/]+")</f>
@@ -5180,16 +5163,16 @@
     </row>
     <row r="38" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B38" s="2">
         <v>0</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>43</v>
@@ -5210,7 +5193,7 @@
         <v>71</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>137</v>
@@ -5234,7 +5217,7 @@
         <v>6</v>
       </c>
       <c r="S38" s="2" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="T38" s="2" t="str" cm="1">
         <f t="array" ref="T38">_xlfn.REGEXEXTRACT(A38,"(?&lt;=//)[^/]+")</f>
@@ -5243,7 +5226,7 @@
     </row>
     <row r="39" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B39" s="2">
         <v>0</v>
@@ -5252,7 +5235,7 @@
         <v>436</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>43</v>
@@ -5276,10 +5259,10 @@
         <v>84</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>152</v>
@@ -5297,7 +5280,7 @@
         <v>6</v>
       </c>
       <c r="S39" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="T39" s="2" t="str" cm="1">
         <f t="array" ref="T39">_xlfn.REGEXEXTRACT(A39,"(?&lt;=//)[^/]+")</f>
@@ -5306,16 +5289,16 @@
     </row>
     <row r="40" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B40" s="2">
         <v>0</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>43</v>
@@ -5327,7 +5310,7 @@
         <v>156</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>60</v>
@@ -5336,13 +5319,13 @@
         <v>84</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>462</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>91</v>
@@ -5360,7 +5343,7 @@
         <v>6</v>
       </c>
       <c r="S40" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="T40" s="2" t="str" cm="1">
         <f t="array" ref="T40">_xlfn.REGEXEXTRACT(A40,"(?&lt;=//)[^/]+")</f>
@@ -5369,16 +5352,16 @@
     </row>
     <row r="41" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B41" s="2">
         <v>0</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>43</v>
@@ -5390,19 +5373,19 @@
         <v>156</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>235</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>412</v>
       </c>
       <c r="L41" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="M41" s="2" t="s">
         <v>60</v>
@@ -5414,7 +5397,7 @@
         <v>91</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="Q41" s="2" t="s">
         <v>56</v>
@@ -5423,7 +5406,7 @@
         <v>6</v>
       </c>
       <c r="S41" s="2" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="T41" s="2" t="str" cm="1">
         <f t="array" ref="T41">_xlfn.REGEXEXTRACT(A41,"(?&lt;=//)[^/]+")</f>
@@ -5432,16 +5415,16 @@
     </row>
     <row r="42" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B42" s="2">
         <v>0</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>43</v>
@@ -5456,19 +5439,19 @@
         <v>60</v>
       </c>
       <c r="I42" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="J42" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="K42" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="K42" s="2" t="s">
+      <c r="L42" s="2" t="s">
         <v>696</v>
       </c>
-      <c r="L42" s="2" t="s">
-        <v>697</v>
-      </c>
       <c r="M42" s="2" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="N42" s="2" t="s">
         <v>91</v>
@@ -5477,7 +5460,7 @@
         <v>315</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="Q42" s="2" t="s">
         <v>56</v>
@@ -5486,7 +5469,7 @@
         <v>6</v>
       </c>
       <c r="S42" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="T42" s="2" t="str" cm="1">
         <f t="array" ref="T42">_xlfn.REGEXEXTRACT(A42,"(?&lt;=//)[^/]+")</f>
@@ -5495,16 +5478,16 @@
     </row>
     <row r="43" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B43" s="2">
         <v>0</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>43</v>
@@ -5516,19 +5499,19 @@
         <v>156</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="I43" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="J43" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="J43" s="2" t="s">
+      <c r="K43" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="K43" s="2" t="s">
+      <c r="L43" s="2" t="s">
         <v>702</v>
-      </c>
-      <c r="L43" s="2" t="s">
-        <v>703</v>
       </c>
       <c r="M43" s="2" t="s">
         <v>343</v>
@@ -5549,7 +5532,7 @@
         <v>6</v>
       </c>
       <c r="S43" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="T43" s="2" t="str" cm="1">
         <f t="array" ref="T43">_xlfn.REGEXEXTRACT(A43,"(?&lt;=//)[^/]+")</f>
@@ -5558,16 +5541,16 @@
     </row>
     <row r="44" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B44" s="2">
         <v>0</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>43</v>
@@ -5612,7 +5595,7 @@
         <v>6</v>
       </c>
       <c r="S44" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="T44" s="2" t="str" cm="1">
         <f t="array" ref="T44">_xlfn.REGEXEXTRACT(A44,"(?&lt;=//)[^/]+")</f>
@@ -5621,16 +5604,16 @@
     </row>
     <row r="45" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B45" s="2">
         <v>51</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>43</v>
@@ -5648,7 +5631,7 @@
         <v>98</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="K45" s="2" t="s">
         <v>343</v>
@@ -5675,7 +5658,7 @@
         <v>6</v>
       </c>
       <c r="S45" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="T45" s="2" t="str" cm="1">
         <f t="array" ref="T45">_xlfn.REGEXEXTRACT(A45,"(?&lt;=//)[^/]+")</f>
@@ -5684,19 +5667,19 @@
     </row>
     <row r="46" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B46" s="2">
         <v>129</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>43</v>
@@ -5705,16 +5688,16 @@
         <v>80</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>137</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>280</v>
@@ -5732,13 +5715,13 @@
         <v>91</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="R46" s="2">
         <v>5</v>
       </c>
       <c r="S46" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="T46" s="2" t="str" cm="1">
         <f t="array" ref="T46">_xlfn.REGEXEXTRACT(A46,"(?&lt;=//)[^/]+")</f>
@@ -5747,19 +5730,19 @@
     </row>
     <row r="47" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B47" s="2">
         <v>128</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>43</v>
@@ -5780,10 +5763,10 @@
         <v>125</v>
       </c>
       <c r="L47" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="M47" s="2" t="s">
         <v>637</v>
-      </c>
-      <c r="M47" s="2" t="s">
-        <v>638</v>
       </c>
       <c r="N47" s="2">
         <v>69</v>
@@ -5801,7 +5784,7 @@
         <v>5</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="T47" s="2" t="str" cm="1">
         <f t="array" ref="T47">_xlfn.REGEXEXTRACT(A47,"(?&lt;=//)[^/]+")</f>
@@ -5810,16 +5793,16 @@
     </row>
     <row r="48" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B48" s="2">
         <v>116</v>
       </c>
       <c r="C48" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>610</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>611</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>43</v>
@@ -5837,10 +5820,10 @@
         <v>113</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>67</v>
@@ -5849,13 +5832,13 @@
         <v>82</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="Q48" s="2" t="s">
         <v>56</v>
@@ -5864,7 +5847,7 @@
         <v>5</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="T48" s="2" t="str" cm="1">
         <f t="array" ref="T48">_xlfn.REGEXEXTRACT(A48,"(?&lt;=//)[^/]+")</f>
@@ -5873,7 +5856,7 @@
     </row>
     <row r="49" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B49" s="2">
         <v>89</v>
@@ -5882,7 +5865,7 @@
         <v>95</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>179</v>
@@ -5897,7 +5880,7 @@
         <v>98</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>71</v>
@@ -5906,19 +5889,19 @@
         <v>137</v>
       </c>
       <c r="L49" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="M49" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="M49" s="2" t="s">
+      <c r="N49" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="N49" s="2" t="s">
+      <c r="O49" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="P49" s="2" t="s">
         <v>606</v>
-      </c>
-      <c r="O49" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="P49" s="2" t="s">
-        <v>607</v>
       </c>
       <c r="Q49" s="2" t="s">
         <v>56</v>
@@ -5927,7 +5910,7 @@
         <v>5</v>
       </c>
       <c r="S49" s="2" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="T49" s="2" t="str" cm="1">
         <f t="array" ref="T49">_xlfn.REGEXEXTRACT(A49,"(?&lt;=//)[^/]+")</f>
@@ -5936,7 +5919,7 @@
     </row>
     <row r="50" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B50" s="2">
         <v>65</v>
@@ -5945,7 +5928,7 @@
         <v>112</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>43</v>
@@ -5981,7 +5964,7 @@
         <v>101</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="Q50" s="2" t="s">
         <v>56</v>
@@ -5990,7 +5973,7 @@
         <v>5</v>
       </c>
       <c r="S50" s="2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="T50" s="2" t="str" cm="1">
         <f t="array" ref="T50">_xlfn.REGEXEXTRACT(A50,"(?&lt;=//)[^/]+")</f>
@@ -5999,7 +5982,7 @@
     </row>
     <row r="51" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B51" s="2">
         <v>62</v>
@@ -6008,7 +5991,7 @@
         <v>112</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>43</v>
@@ -6032,7 +6015,7 @@
         <v>71</v>
       </c>
       <c r="L51" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="M51" s="2" t="s">
         <v>117</v>
@@ -6053,7 +6036,7 @@
         <v>5</v>
       </c>
       <c r="S51" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="T51" s="2" t="str" cm="1">
         <f t="array" ref="T51">_xlfn.REGEXEXTRACT(A51,"(?&lt;=//)[^/]+")</f>
@@ -6062,7 +6045,7 @@
     </row>
     <row r="52" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B52" s="2">
         <v>60</v>
@@ -6071,7 +6054,7 @@
         <v>468</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>43</v>
@@ -6104,7 +6087,7 @@
         <v>90</v>
       </c>
       <c r="O52" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="P52" s="2" t="s">
         <v>435</v>
@@ -6116,7 +6099,7 @@
         <v>5</v>
       </c>
       <c r="S52" s="2" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="T52" s="2" t="str" cm="1">
         <f t="array" ref="T52">_xlfn.REGEXEXTRACT(A52,"(?&lt;=//)[^/]+")</f>
@@ -6278,22 +6261,22 @@
         <v>117</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>125</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="N55" s="2" t="s">
         <v>380</v>
       </c>
       <c r="O55" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="P55" s="2" t="s">
         <v>68</v>
@@ -6305,7 +6288,7 @@
         <v>5</v>
       </c>
       <c r="S55" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="T55" s="2" t="str" cm="1">
         <f t="array" ref="T55">_xlfn.REGEXEXTRACT(A55,"(?&lt;=//)[^/]+")</f>
@@ -6320,10 +6303,10 @@
         <v>55</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>43</v>
@@ -6335,13 +6318,13 @@
         <v>81</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>82</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>116</v>
@@ -6353,13 +6336,13 @@
         <v>425</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="O56" s="2" t="s">
         <v>453</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="Q56" s="2" t="s">
         <v>56</v>
@@ -6368,7 +6351,7 @@
         <v>5</v>
       </c>
       <c r="S56" s="2" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="T56" s="2" t="str" cm="1">
         <f t="array" ref="T56">_xlfn.REGEXEXTRACT(A56,"(?&lt;=//)[^/]+")</f>
@@ -6416,7 +6399,7 @@
         <v>466</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>435</v>
@@ -6566,7 +6549,7 @@
     </row>
     <row r="60" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B60" s="2">
         <v>46</v>
@@ -6575,7 +6558,7 @@
         <v>436</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>43</v>
@@ -6587,16 +6570,16 @@
         <v>80</v>
       </c>
       <c r="H60" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="I60" s="2" t="s">
         <v>760</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>761</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>84</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>67</v>
@@ -6620,7 +6603,7 @@
         <v>5</v>
       </c>
       <c r="S60" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="T60" s="2" t="str" cm="1">
         <f t="array" ref="T60">_xlfn.REGEXEXTRACT(A60,"(?&lt;=//)[^/]+")</f>
@@ -6650,7 +6633,7 @@
         <v>80</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>82</v>
@@ -6671,7 +6654,7 @@
         <v>380</v>
       </c>
       <c r="O61" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="P61" s="2" t="s">
         <v>112</v>
@@ -6902,7 +6885,7 @@
         <v>80</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>70</v>
@@ -6944,16 +6927,16 @@
     </row>
     <row r="66" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B66" s="2">
         <v>14</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>43</v>
@@ -6968,7 +6951,7 @@
         <v>420</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>60</v>
@@ -6977,7 +6960,7 @@
         <v>462</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="M66" s="2" t="s">
         <v>235</v>
@@ -6998,7 +6981,7 @@
         <v>5</v>
       </c>
       <c r="S66" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="T66" s="2" t="str" cm="1">
         <f t="array" ref="T66">_xlfn.REGEXEXTRACT(A66,"(?&lt;=//)[^/]+")</f>
@@ -7007,25 +6990,25 @@
     </row>
     <row r="67" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B67" s="2">
         <v>11</v>
       </c>
       <c r="C67" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G67" s="2" t="s">
         <v>733</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>734</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>226</v>
@@ -7034,7 +7017,7 @@
         <v>66</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>65</v>
@@ -7061,7 +7044,7 @@
         <v>5</v>
       </c>
       <c r="S67" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="T67" s="2" t="str" cm="1">
         <f t="array" ref="T67">_xlfn.REGEXEXTRACT(A67,"(?&lt;=//)[^/]+")</f>
@@ -7124,7 +7107,7 @@
         <v>5</v>
       </c>
       <c r="S68" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="T68" s="2" t="str" cm="1">
         <f t="array" ref="T68">_xlfn.REGEXEXTRACT(A68,"(?&lt;=//)[^/]+")</f>
@@ -7196,16 +7179,16 @@
     </row>
     <row r="70" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B70" s="2">
         <v>1</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>43</v>
@@ -7226,7 +7209,7 @@
         <v>116</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="L70" s="2" t="s">
         <v>43</v>
@@ -7235,7 +7218,7 @@
         <v>43</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="O70" s="2" t="s">
         <v>43</v>
@@ -7244,13 +7227,13 @@
         <v>43</v>
       </c>
       <c r="Q70" s="2" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="R70" s="2">
         <v>5</v>
       </c>
       <c r="S70" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="T70" s="2" t="str" cm="1">
         <f t="array" ref="T70">_xlfn.REGEXEXTRACT(A70,"(?&lt;=//)[^/]+")</f>
@@ -7259,16 +7242,16 @@
     </row>
     <row r="71" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B71" s="2">
         <v>0</v>
       </c>
       <c r="C71" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="D71" s="2" t="s">
         <v>670</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>671</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>43</v>
@@ -7286,10 +7269,10 @@
         <v>65</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>226</v>
@@ -7313,7 +7296,7 @@
         <v>5</v>
       </c>
       <c r="S71" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="T71" s="2" t="str" cm="1">
         <f t="array" ref="T71">_xlfn.REGEXEXTRACT(A71,"(?&lt;=//)[^/]+")</f>
@@ -7322,16 +7305,16 @@
     </row>
     <row r="72" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B72" s="2">
         <v>0</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>43</v>
@@ -7346,19 +7329,19 @@
         <v>171</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="J72" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="K72" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="K72" s="2" t="s">
+      <c r="L72" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="L72" s="2" t="s">
+      <c r="M72" s="2" t="s">
         <v>708</v>
-      </c>
-      <c r="M72" s="2" t="s">
-        <v>709</v>
       </c>
       <c r="N72" s="2" t="s">
         <v>91</v>
@@ -7367,7 +7350,7 @@
         <v>68</v>
       </c>
       <c r="P72" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="Q72" s="2" t="s">
         <v>56</v>
@@ -7376,7 +7359,7 @@
         <v>5</v>
       </c>
       <c r="S72" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="T72" s="2" t="str" cm="1">
         <f t="array" ref="T72">_xlfn.REGEXEXTRACT(A72,"(?&lt;=//)[^/]+")</f>
@@ -7385,16 +7368,16 @@
     </row>
     <row r="73" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="B73" s="2">
         <v>47</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>43</v>
@@ -7424,13 +7407,13 @@
         <v>43</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="O73" s="2" t="s">
         <v>91</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="Q73" s="2" t="s">
         <v>56</v>
@@ -7439,7 +7422,7 @@
         <v>5</v>
       </c>
       <c r="S73" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="T73" s="2" t="str" cm="1">
         <f t="array" ref="T73">_xlfn.REGEXEXTRACT(A73,"(?&lt;=//)[^/]+")</f>
@@ -7448,19 +7431,19 @@
     </row>
     <row r="74" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B74" s="2">
         <v>44</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D74" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="E74" s="2" t="s">
         <v>780</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>781</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>43</v>
@@ -7484,10 +7467,10 @@
         <v>60</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="O74" s="2" t="s">
         <v>91</v>
@@ -7502,7 +7485,7 @@
         <v>5</v>
       </c>
       <c r="S74" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="T74" s="2" t="str" cm="1">
         <f t="array" ref="T74">_xlfn.REGEXEXTRACT(A74,"(?&lt;=//)[^/]+")</f>
@@ -7511,16 +7494,16 @@
     </row>
     <row r="75" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>653</v>
+        <v>794</v>
       </c>
       <c r="B75" s="2">
-        <v>182</v>
+        <v>54</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>685</v>
+        <v>154</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>685</v>
+        <v>795</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>43</v>
@@ -7529,97 +7512,97 @@
         <v>43</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>587</v>
+        <v>117</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>605</v>
+        <v>98</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>65</v>
+        <v>466</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>428</v>
+        <v>60</v>
       </c>
       <c r="L75" s="2" t="s">
-        <v>654</v>
+        <v>234</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>655</v>
+        <v>343</v>
       </c>
       <c r="N75" s="2" t="s">
         <v>152</v>
       </c>
       <c r="O75" s="2" t="s">
-        <v>656</v>
+        <v>91</v>
       </c>
       <c r="P75" s="2" t="s">
-        <v>657</v>
+        <v>43</v>
       </c>
       <c r="Q75" s="2" t="s">
         <v>56</v>
       </c>
       <c r="R75" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S75" s="2" t="s">
-        <v>658</v>
+        <v>796</v>
       </c>
       <c r="T75" s="2" t="str" cm="1">
         <f t="array" ref="T75">_xlfn.REGEXEXTRACT(A75,"(?&lt;=//)[^/]+")</f>
-        <v>punishbang.com</v>
+        <v>www.porntry.com</v>
       </c>
     </row>
     <row r="76" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="B76" s="2">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>646</v>
+        <v>684</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>647</v>
+        <v>684</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>648</v>
+        <v>43</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>476</v>
+        <v>586</v>
       </c>
       <c r="I76" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="J76" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K76" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="J76" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="K76" s="2" t="s">
-        <v>649</v>
-      </c>
       <c r="L76" s="2" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="N76" s="2" t="s">
         <v>152</v>
       </c>
       <c r="O76" s="2" t="s">
-        <v>592</v>
+        <v>655</v>
       </c>
       <c r="P76" s="2" t="s">
-        <v>453</v>
+        <v>656</v>
       </c>
       <c r="Q76" s="2" t="s">
         <v>56</v>
@@ -7628,7 +7611,7 @@
         <v>4</v>
       </c>
       <c r="S76" s="2" t="s">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="T76" s="2" t="str" cm="1">
         <f t="array" ref="T76">_xlfn.REGEXEXTRACT(A76,"(?&lt;=//)[^/]+")</f>
@@ -7637,19 +7620,19 @@
     </row>
     <row r="77" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>225</v>
+        <v>644</v>
       </c>
       <c r="B77" s="2">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>222</v>
+        <v>645</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>397</v>
+        <v>646</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>403</v>
+        <v>647</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>43</v>
@@ -7658,31 +7641,31 @@
         <v>81</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>226</v>
+        <v>476</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>93</v>
+        <v>428</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>228</v>
+        <v>117</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>43</v>
+        <v>648</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>43</v>
+        <v>649</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>43</v>
+        <v>650</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>519</v>
+        <v>152</v>
       </c>
       <c r="O77" s="2" t="s">
-        <v>152</v>
+        <v>591</v>
       </c>
       <c r="P77" s="2" t="s">
-        <v>159</v>
+        <v>453</v>
       </c>
       <c r="Q77" s="2" t="s">
         <v>56</v>
@@ -7691,55 +7674,55 @@
         <v>4</v>
       </c>
       <c r="S77" s="2" t="s">
-        <v>227</v>
+        <v>651</v>
       </c>
       <c r="T77" s="2" t="str" cm="1">
         <f t="array" ref="T77">_xlfn.REGEXEXTRACT(A77,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
+        <v>punishbang.com</v>
       </c>
     </row>
     <row r="78" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>35</v>
+        <v>225</v>
       </c>
       <c r="B78" s="2">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>154</v>
+        <v>222</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>155</v>
+        <v>397</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>43</v>
+        <v>403</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>156</v>
+        <v>81</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>157</v>
+        <v>226</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>158</v>
+        <v>93</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>98</v>
+        <v>228</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>160</v>
+        <v>43</v>
       </c>
       <c r="M78" s="2" t="s">
         <v>43</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>149</v>
+        <v>518</v>
       </c>
       <c r="O78" s="2" t="s">
         <v>152</v>
@@ -7754,25 +7737,25 @@
         <v>4</v>
       </c>
       <c r="S78" s="2" t="s">
-        <v>161</v>
+        <v>227</v>
       </c>
       <c r="T78" s="2" t="str" cm="1">
         <f t="array" ref="T78">_xlfn.REGEXEXTRACT(A78,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="79" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>pornxp.com</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>615</v>
+        <v>35</v>
       </c>
       <c r="B79" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>616</v>
+        <v>154</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>617</v>
+        <v>155</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>43</v>
@@ -7781,34 +7764,34 @@
         <v>43</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>320</v>
+        <v>156</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>618</v>
+        <v>157</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>292</v>
+        <v>158</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>428</v>
+        <v>98</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>619</v>
+        <v>160</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>620</v>
+        <v>43</v>
       </c>
       <c r="N79" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="O79" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="O79" s="2" t="s">
-        <v>621</v>
-      </c>
       <c r="P79" s="2" t="s">
-        <v>622</v>
+        <v>159</v>
       </c>
       <c r="Q79" s="2" t="s">
         <v>56</v>
@@ -7817,61 +7800,61 @@
         <v>4</v>
       </c>
       <c r="S79" s="2" t="s">
-        <v>623</v>
+        <v>161</v>
       </c>
       <c r="T79" s="2" t="str" cm="1">
         <f t="array" ref="T79">_xlfn.REGEXEXTRACT(A79,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
-      </c>
-    </row>
-    <row r="80" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>559</v>
+        <v>614</v>
       </c>
       <c r="B80" s="2">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>273</v>
+        <v>615</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>560</v>
+        <v>616</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>561</v>
+        <v>43</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>110</v>
+        <v>617</v>
       </c>
       <c r="I80" s="2" t="s">
-        <v>67</v>
+        <v>292</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>98</v>
+        <v>428</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>466</v>
+        <v>84</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>125</v>
+        <v>618</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>137</v>
+        <v>619</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>152</v>
       </c>
       <c r="O80" s="2" t="s">
-        <v>91</v>
+        <v>620</v>
       </c>
       <c r="P80" s="2" t="s">
-        <v>519</v>
+        <v>621</v>
       </c>
       <c r="Q80" s="2" t="s">
         <v>56</v>
@@ -7880,61 +7863,61 @@
         <v>4</v>
       </c>
       <c r="S80" s="2" t="s">
-        <v>562</v>
+        <v>622</v>
       </c>
       <c r="T80" s="2" t="str" cm="1">
         <f t="array" ref="T80">_xlfn.REGEXEXTRACT(A80,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="81" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+        <v>m.hqporner.com</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>16</v>
+        <v>558</v>
       </c>
       <c r="B81" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>223</v>
+        <v>273</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>395</v>
+        <v>559</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>401</v>
+        <v>560</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>343</v>
+        <v>466</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>88</v>
+        <v>137</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>90</v>
+        <v>152</v>
       </c>
       <c r="O81" s="2" t="s">
         <v>91</v>
       </c>
       <c r="P81" s="2" t="s">
-        <v>92</v>
+        <v>518</v>
       </c>
       <c r="Q81" s="2" t="s">
         <v>56</v>
@@ -7943,28 +7926,28 @@
         <v>4</v>
       </c>
       <c r="S81" s="2" t="s">
-        <v>94</v>
+        <v>561</v>
       </c>
       <c r="T81" s="2" t="str" cm="1">
         <f t="array" ref="T81">_xlfn.REGEXEXTRACT(A81,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="82" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>532</v>
+        <v>16</v>
       </c>
       <c r="B82" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>95</v>
+        <v>223</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>533</v>
+        <v>395</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>534</v>
+        <v>401</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>43</v>
@@ -7973,31 +7956,31 @@
         <v>81</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="I82" s="2" t="s">
-        <v>535</v>
+        <v>82</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>536</v>
+        <v>83</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>97</v>
+        <v>343</v>
       </c>
       <c r="L82" s="2" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="N82" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="O82" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="P82" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="O82" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="P82" s="2" t="s">
-        <v>519</v>
       </c>
       <c r="Q82" s="2" t="s">
         <v>56</v>
@@ -8006,61 +7989,61 @@
         <v>4</v>
       </c>
       <c r="S82" s="2" t="s">
-        <v>537</v>
+        <v>94</v>
       </c>
       <c r="T82" s="2" t="str" cm="1">
         <f t="array" ref="T82">_xlfn.REGEXEXTRACT(A82,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="83" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>20</v>
+        <v>531</v>
       </c>
       <c r="B83" s="2">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>393</v>
+        <v>532</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>43</v>
+        <v>533</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="I83" s="2" t="s">
-        <v>137</v>
+        <v>534</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>406</v>
+        <v>535</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="L83" s="2" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="O83" s="2" t="s">
-        <v>114</v>
+        <v>315</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>43</v>
+        <v>518</v>
       </c>
       <c r="Q83" s="2" t="s">
         <v>56</v>
@@ -8069,25 +8052,25 @@
         <v>4</v>
       </c>
       <c r="S83" s="2" t="s">
-        <v>115</v>
+        <v>536</v>
       </c>
       <c r="T83" s="2" t="str" cm="1">
         <f t="array" ref="T83">_xlfn.REGEXEXTRACT(A83,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="84" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="B84" s="2">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>383</v>
+        <v>111</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>177</v>
+        <v>393</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>43</v>
@@ -8096,34 +8079,34 @@
         <v>43</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>486</v>
+        <v>116</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>341</v>
+        <v>137</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>487</v>
+        <v>406</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="L84" s="2" t="s">
-        <v>476</v>
+        <v>113</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="N84" s="2">
-        <v>69</v>
+        <v>65</v>
+      </c>
+      <c r="N84" s="2" t="s">
+        <v>112</v>
       </c>
       <c r="O84" s="2" t="s">
-        <v>190</v>
+        <v>114</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>490</v>
+        <v>43</v>
       </c>
       <c r="Q84" s="2" t="s">
         <v>56</v>
@@ -8132,61 +8115,61 @@
         <v>4</v>
       </c>
       <c r="S84" s="2" t="s">
-        <v>488</v>
+        <v>115</v>
       </c>
       <c r="T84" s="2" t="str" cm="1">
         <f t="array" ref="T84">_xlfn.REGEXEXTRACT(A84,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="85" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B85" s="2">
         <v>53</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>112</v>
+        <v>383</v>
       </c>
       <c r="D85" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H85" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="E85" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G85" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>306</v>
-      </c>
       <c r="I85" s="2" t="s">
-        <v>67</v>
+        <v>341</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>345</v>
+        <v>486</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>427</v>
+        <v>98</v>
       </c>
       <c r="L85" s="2" t="s">
-        <v>65</v>
+        <v>476</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="N85" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
+      </c>
+      <c r="N85" s="2">
+        <v>69</v>
       </c>
       <c r="O85" s="2" t="s">
-        <v>492</v>
+        <v>190</v>
       </c>
       <c r="P85" s="2" t="s">
-        <v>101</v>
+        <v>489</v>
       </c>
       <c r="Q85" s="2" t="s">
         <v>56</v>
@@ -8195,7 +8178,7 @@
         <v>4</v>
       </c>
       <c r="S85" s="2" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="T85" s="2" t="str" cm="1">
         <f t="array" ref="T85">_xlfn.REGEXEXTRACT(A85,"(?&lt;=//)[^/]+")</f>
@@ -8204,16 +8187,16 @@
     </row>
     <row r="86" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B86" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>301</v>
+        <v>112</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>685</v>
+        <v>484</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>43</v>
@@ -8225,16 +8208,16 @@
         <v>80</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>280</v>
+        <v>306</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>123</v>
+        <v>67</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>98</v>
+        <v>345</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>82</v>
+        <v>427</v>
       </c>
       <c r="L86" s="2" t="s">
         <v>65</v>
@@ -8243,13 +8226,13 @@
         <v>117</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>112</v>
+        <v>490</v>
       </c>
       <c r="O86" s="2" t="s">
-        <v>478</v>
+        <v>491</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>152</v>
+        <v>101</v>
       </c>
       <c r="Q86" s="2" t="s">
         <v>56</v>
@@ -8258,25 +8241,25 @@
         <v>4</v>
       </c>
       <c r="S86" s="2" t="s">
-        <v>479</v>
+        <v>492</v>
       </c>
       <c r="T86" s="2" t="str" cm="1">
         <f t="array" ref="T86">_xlfn.REGEXEXTRACT(A86,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.party</v>
-      </c>
-    </row>
-    <row r="87" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="B87" s="2">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>111</v>
+        <v>301</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>439</v>
+        <v>684</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>43</v>
@@ -8288,31 +8271,31 @@
         <v>80</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>407</v>
+        <v>280</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>406</v>
+        <v>98</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>441</v>
+        <v>82</v>
       </c>
       <c r="L87" s="2" t="s">
-        <v>442</v>
+        <v>65</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>428</v>
+        <v>117</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>440</v>
+        <v>112</v>
       </c>
       <c r="O87" s="2" t="s">
-        <v>190</v>
+        <v>478</v>
       </c>
       <c r="P87" s="2" t="s">
-        <v>43</v>
+        <v>152</v>
       </c>
       <c r="Q87" s="2" t="s">
         <v>56</v>
@@ -8321,25 +8304,25 @@
         <v>4</v>
       </c>
       <c r="S87" s="2" t="s">
-        <v>443</v>
+        <v>479</v>
       </c>
       <c r="T87" s="2" t="str" cm="1">
         <f t="array" ref="T87">_xlfn.REGEXEXTRACT(A87,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="88" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+        <v>spankbang.party</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="B88" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>43</v>
@@ -8351,31 +8334,31 @@
         <v>80</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="I88" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="M88" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="J88" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="K88" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L88" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="M88" s="2" t="s">
-        <v>430</v>
-      </c>
       <c r="N88" s="2" t="s">
-        <v>152</v>
+        <v>440</v>
       </c>
       <c r="O88" s="2" t="s">
-        <v>429</v>
+        <v>190</v>
       </c>
       <c r="P88" s="2" t="s">
-        <v>112</v>
+        <v>43</v>
       </c>
       <c r="Q88" s="2" t="s">
         <v>56</v>
@@ -8384,7 +8367,7 @@
         <v>4</v>
       </c>
       <c r="S88" s="2" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="T88" s="2" t="str" cm="1">
         <f t="array" ref="T88">_xlfn.REGEXEXTRACT(A88,"(?&lt;=//)[^/]+")</f>
@@ -8393,16 +8376,16 @@
     </row>
     <row r="89" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B89" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>43</v>
@@ -8414,31 +8397,31 @@
         <v>80</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>406</v>
+        <v>427</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>407</v>
+        <v>428</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>306</v>
+        <v>76</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>409</v>
+        <v>98</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>412</v>
+        <v>113</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>410</v>
+        <v>430</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>408</v>
+        <v>152</v>
       </c>
       <c r="O89" s="2" t="s">
-        <v>375</v>
+        <v>429</v>
       </c>
       <c r="P89" s="2" t="s">
-        <v>380</v>
+        <v>112</v>
       </c>
       <c r="Q89" s="2" t="s">
         <v>56</v>
@@ -8447,7 +8430,7 @@
         <v>4</v>
       </c>
       <c r="S89" s="2" t="s">
-        <v>411</v>
+        <v>431</v>
       </c>
       <c r="T89" s="2" t="str" cm="1">
         <f t="array" ref="T89">_xlfn.REGEXEXTRACT(A89,"(?&lt;=//)[^/]+")</f>
@@ -8456,52 +8439,52 @@
     </row>
     <row r="90" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>255</v>
+        <v>11</v>
       </c>
       <c r="B90" s="2">
         <v>44</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>685</v>
+        <v>111</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>416</v>
+        <v>405</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>418</v>
+        <v>43</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>417</v>
+        <v>80</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>123</v>
+        <v>406</v>
       </c>
       <c r="I90" s="2" t="s">
-        <v>67</v>
+        <v>407</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>420</v>
+        <v>306</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>65</v>
+        <v>409</v>
       </c>
       <c r="L90" s="2" t="s">
-        <v>93</v>
+        <v>412</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>83</v>
+        <v>410</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>152</v>
+        <v>408</v>
       </c>
       <c r="O90" s="2" t="s">
-        <v>90</v>
+        <v>375</v>
       </c>
       <c r="P90" s="2" t="s">
-        <v>421</v>
+        <v>380</v>
       </c>
       <c r="Q90" s="2" t="s">
         <v>56</v>
@@ -8510,61 +8493,61 @@
         <v>4</v>
       </c>
       <c r="S90" s="2" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="T90" s="2" t="str" cm="1">
         <f t="array" ref="T90">_xlfn.REGEXEXTRACT(A90,"(?&lt;=//)[^/]+")</f>
-        <v>txxx.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="91" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="B91" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>95</v>
+        <v>684</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>371</v>
+        <v>416</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>43</v>
+        <v>418</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>80</v>
+        <v>417</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>71</v>
+        <v>123</v>
       </c>
       <c r="I91" s="2" t="s">
-        <v>373</v>
+        <v>67</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>98</v>
+        <v>420</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>125</v>
+        <v>65</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>43</v>
+        <v>93</v>
       </c>
       <c r="M91" s="2" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>374</v>
+        <v>152</v>
       </c>
       <c r="O91" s="2" t="s">
-        <v>372</v>
+        <v>90</v>
       </c>
       <c r="P91" s="2" t="s">
-        <v>43</v>
+        <v>421</v>
       </c>
       <c r="Q91" s="2" t="s">
         <v>56</v>
@@ -8573,25 +8556,25 @@
         <v>4</v>
       </c>
       <c r="S91" s="2" t="s">
-        <v>376</v>
+        <v>419</v>
       </c>
       <c r="T91" s="2" t="str" cm="1">
         <f t="array" ref="T91">_xlfn.REGEXEXTRACT(A91,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>txxx.com</v>
       </c>
     </row>
     <row r="92" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>31</v>
+        <v>242</v>
       </c>
       <c r="B92" s="2">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>177</v>
+        <v>371</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>43</v>
@@ -8603,28 +8586,28 @@
         <v>80</v>
       </c>
       <c r="H92" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="J92" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="I92" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="J92" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="K92" s="2" t="s">
-        <v>67</v>
+        <v>125</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="M92" s="2" t="s">
         <v>43</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>128</v>
+        <v>374</v>
       </c>
       <c r="O92" s="2" t="s">
-        <v>130</v>
+        <v>372</v>
       </c>
       <c r="P92" s="2" t="s">
         <v>43</v>
@@ -8636,25 +8619,25 @@
         <v>4</v>
       </c>
       <c r="S92" s="2" t="s">
-        <v>272</v>
+        <v>376</v>
       </c>
       <c r="T92" s="2" t="str" cm="1">
         <f t="array" ref="T92">_xlfn.REGEXEXTRACT(A92,"(?&lt;=//)[^/]+")</f>
         <v>bdsmstreak.com</v>
       </c>
     </row>
-    <row r="93" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>267</v>
+        <v>31</v>
       </c>
       <c r="B93" s="2">
         <v>36</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>314</v>
+        <v>127</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>351</v>
+        <v>177</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>43</v>
@@ -8663,34 +8646,34 @@
         <v>43</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>353</v>
+        <v>98</v>
       </c>
       <c r="I93" s="2" t="s">
-        <v>354</v>
+        <v>117</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>332</v>
+        <v>129</v>
       </c>
       <c r="K93" s="2" t="s">
-        <v>280</v>
+        <v>67</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="M93" s="2" t="s">
         <v>43</v>
       </c>
       <c r="N93" s="2" t="s">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="O93" s="2" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="P93" s="2" t="s">
-        <v>330</v>
+        <v>43</v>
       </c>
       <c r="Q93" s="2" t="s">
         <v>56</v>
@@ -8699,25 +8682,25 @@
         <v>4</v>
       </c>
       <c r="S93" s="2" t="s">
-        <v>352</v>
+        <v>272</v>
       </c>
       <c r="T93" s="2" t="str" cm="1">
         <f t="array" ref="T93">_xlfn.REGEXEXTRACT(A93,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
-      </c>
-    </row>
-    <row r="94" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="94" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="B94" s="2">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>333</v>
+        <v>314</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>43</v>
@@ -8726,34 +8709,34 @@
         <v>43</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>66</v>
+        <v>353</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>335</v>
+        <v>354</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>125</v>
+        <v>332</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>252</v>
+        <v>280</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>339</v>
+        <v>43</v>
       </c>
       <c r="M94" s="2" t="s">
         <v>43</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>152</v>
+        <v>91</v>
       </c>
       <c r="O94" s="2" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="P94" s="2" t="s">
-        <v>43</v>
+        <v>330</v>
       </c>
       <c r="Q94" s="2" t="s">
         <v>56</v>
@@ -8762,58 +8745,58 @@
         <v>4</v>
       </c>
       <c r="S94" s="2" t="s">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="T94" s="2" t="str" cm="1">
         <f t="array" ref="T94">_xlfn.REGEXEXTRACT(A94,"(?&lt;=//)[^/]+")</f>
-        <v>txxx.me</v>
+        <v>pornxp.com</v>
       </c>
     </row>
     <row r="95" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
       <c r="B95" s="2">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>95</v>
+        <v>333</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>389</v>
+        <v>334</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>179</v>
+        <v>43</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>80</v>
+        <v>325</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>98</v>
+        <v>335</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>332</v>
+        <v>252</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>65</v>
+        <v>339</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>425</v>
+        <v>43</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>190</v>
+        <v>152</v>
       </c>
       <c r="O95" s="2" t="s">
-        <v>92</v>
+        <v>43</v>
       </c>
       <c r="P95" s="2" t="s">
         <v>43</v>
@@ -8825,61 +8808,61 @@
         <v>4</v>
       </c>
       <c r="S95" s="2" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="T95" s="2" t="str" cm="1">
         <f t="array" ref="T95">_xlfn.REGEXEXTRACT(A95,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>txxx.me</v>
       </c>
     </row>
     <row r="96" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>751</v>
+        <v>245</v>
       </c>
       <c r="B96" s="2">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>230</v>
+        <v>95</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>752</v>
+        <v>389</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>43</v>
+        <v>179</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>156</v>
+        <v>80</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>753</v>
+        <v>113</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>158</v>
+        <v>76</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>98</v>
+        <v>332</v>
       </c>
       <c r="L96" s="2" t="s">
-        <v>754</v>
+        <v>65</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>707</v>
+        <v>425</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>683</v>
+        <v>190</v>
       </c>
       <c r="O96" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P96" s="2" t="s">
-        <v>380</v>
+        <v>43</v>
       </c>
       <c r="Q96" s="2" t="s">
         <v>56</v>
@@ -8888,7 +8871,7 @@
         <v>4</v>
       </c>
       <c r="S96" s="2" t="s">
-        <v>755</v>
+        <v>313</v>
       </c>
       <c r="T96" s="2" t="str" cm="1">
         <f t="array" ref="T96">_xlfn.REGEXEXTRACT(A96,"(?&lt;=//)[^/]+")</f>
@@ -8897,16 +8880,16 @@
     </row>
     <row r="97" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>263</v>
+        <v>750</v>
       </c>
       <c r="B97" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>301</v>
+        <v>230</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>300</v>
+        <v>751</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>43</v>
@@ -8915,34 +8898,34 @@
         <v>43</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>117</v>
+        <v>752</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>82</v>
       </c>
       <c r="J97" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="K97" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="K97" s="2" t="s">
-        <v>65</v>
-      </c>
       <c r="L97" s="2" t="s">
-        <v>43</v>
+        <v>753</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>43</v>
+        <v>706</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>112</v>
+        <v>682</v>
       </c>
       <c r="O97" s="2" t="s">
-        <v>303</v>
+        <v>91</v>
       </c>
       <c r="P97" s="2" t="s">
-        <v>43</v>
+        <v>380</v>
       </c>
       <c r="Q97" s="2" t="s">
         <v>56</v>
@@ -8951,7 +8934,7 @@
         <v>4</v>
       </c>
       <c r="S97" s="2" t="s">
-        <v>304</v>
+        <v>754</v>
       </c>
       <c r="T97" s="2" t="str" cm="1">
         <f t="array" ref="T97">_xlfn.REGEXEXTRACT(A97,"(?&lt;=//)[^/]+")</f>
@@ -8960,16 +8943,16 @@
     </row>
     <row r="98" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>4</v>
+        <v>263</v>
       </c>
       <c r="B98" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C98" s="2" t="s">
         <v>301</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>43</v>
@@ -8981,28 +8964,28 @@
         <v>80</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>332</v>
+        <v>82</v>
       </c>
       <c r="J98" s="2" t="s">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="K98" s="2" t="s">
-        <v>591</v>
+        <v>65</v>
       </c>
       <c r="L98" s="2" t="s">
-        <v>280</v>
+        <v>43</v>
       </c>
       <c r="M98" s="2" t="s">
         <v>43</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>375</v>
+        <v>112</v>
       </c>
       <c r="O98" s="2" t="s">
-        <v>43</v>
+        <v>303</v>
       </c>
       <c r="P98" s="2" t="s">
         <v>43</v>
@@ -9014,7 +8997,7 @@
         <v>4</v>
       </c>
       <c r="S98" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="T98" s="2" t="str" cm="1">
         <f t="array" ref="T98">_xlfn.REGEXEXTRACT(A98,"(?&lt;=//)[^/]+")</f>
@@ -9023,16 +9006,16 @@
     </row>
     <row r="99" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>268</v>
+        <v>4</v>
       </c>
       <c r="B99" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>131</v>
+        <v>299</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>43</v>
@@ -9041,34 +9024,34 @@
         <v>43</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>84</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>83</v>
+        <v>332</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>332</v>
+        <v>125</v>
       </c>
       <c r="K99" s="2" t="s">
-        <v>43</v>
+        <v>590</v>
       </c>
       <c r="L99" s="2" t="s">
-        <v>43</v>
+        <v>280</v>
       </c>
       <c r="M99" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="N99" s="2">
-        <v>69</v>
-      </c>
-      <c r="O99" s="2">
-        <v>619</v>
+      <c r="N99" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="O99" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="P99" s="2" t="s">
-        <v>357</v>
+        <v>43</v>
       </c>
       <c r="Q99" s="2" t="s">
         <v>56</v>
@@ -9077,25 +9060,25 @@
         <v>4</v>
       </c>
       <c r="S99" s="2" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="T99" s="2" t="str" cm="1">
         <f t="array" ref="T99">_xlfn.REGEXEXTRACT(A99,"(?&lt;=//)[^/]+")</f>
-        <v>www.porndead.org</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="100" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="B100" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>387</v>
+        <v>290</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>278</v>
+        <v>131</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>43</v>
@@ -9104,17 +9087,17 @@
         <v>43</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>84</v>
       </c>
       <c r="I100" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J100" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="J100" s="2" t="s">
-        <v>294</v>
-      </c>
       <c r="K100" s="2" t="s">
         <v>43</v>
       </c>
@@ -9124,14 +9107,14 @@
       <c r="M100" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="N100" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="O100" s="2" t="s">
-        <v>92</v>
+      <c r="N100" s="2">
+        <v>69</v>
+      </c>
+      <c r="O100" s="2">
+        <v>619</v>
       </c>
       <c r="P100" s="2" t="s">
-        <v>91</v>
+        <v>357</v>
       </c>
       <c r="Q100" s="2" t="s">
         <v>56</v>
@@ -9140,25 +9123,25 @@
         <v>4</v>
       </c>
       <c r="S100" s="2" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="T100" s="2" t="str" cm="1">
         <f t="array" ref="T100">_xlfn.REGEXEXTRACT(A100,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster18.desi</v>
-      </c>
-    </row>
-    <row r="101" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>www.porndead.org</v>
+      </c>
+    </row>
+    <row r="101" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>554</v>
+        <v>0</v>
       </c>
       <c r="B101" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>767</v>
+        <v>387</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>544</v>
+        <v>278</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>43</v>
@@ -9167,16 +9150,16 @@
         <v>43</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>715</v>
+        <v>321</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>43</v>
+        <v>332</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>43</v>
+        <v>294</v>
       </c>
       <c r="K101" s="2" t="s">
         <v>43</v>
@@ -9188,13 +9171,13 @@
         <v>43</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>43</v>
+        <v>282</v>
       </c>
       <c r="O101" s="2" t="s">
-        <v>43</v>
+        <v>92</v>
       </c>
       <c r="P101" s="2" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="Q101" s="2" t="s">
         <v>56</v>
@@ -9203,25 +9186,25 @@
         <v>4</v>
       </c>
       <c r="S101" s="2" t="s">
-        <v>555</v>
+        <v>281</v>
       </c>
       <c r="T101" s="2" t="str" cm="1">
         <f t="array" ref="T101">_xlfn.REGEXEXTRACT(A101,"(?&lt;=//)[^/]+")</f>
-        <v>netfapx.net</v>
+        <v>xhamster18.desi</v>
       </c>
     </row>
     <row r="102" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B102" s="2">
         <v>0</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>43</v>
@@ -9230,7 +9213,7 @@
         <v>43</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>43</v>
@@ -9266,25 +9249,25 @@
         <v>4</v>
       </c>
       <c r="S102" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="T102" s="2" t="str" cm="1">
         <f t="array" ref="T102">_xlfn.REGEXEXTRACT(A102,"(?&lt;=//)[^/]+")</f>
-        <v>pornzog</v>
-      </c>
-    </row>
-    <row r="103" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+        <v>netfapx.net</v>
+      </c>
+    </row>
+    <row r="103" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>673</v>
+        <v>555</v>
       </c>
       <c r="B103" s="2">
         <v>0</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>43</v>
@@ -9293,61 +9276,61 @@
         <v>43</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>156</v>
+        <v>714</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>643</v>
+        <v>43</v>
       </c>
       <c r="I103" s="2" t="s">
-        <v>660</v>
+        <v>43</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>661</v>
+        <v>43</v>
       </c>
       <c r="K103" s="2" t="s">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>292</v>
+        <v>43</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>435</v>
+        <v>43</v>
       </c>
       <c r="O103" s="2" t="s">
-        <v>130</v>
+        <v>43</v>
       </c>
       <c r="P103" s="2" t="s">
-        <v>380</v>
+        <v>43</v>
       </c>
       <c r="Q103" s="2" t="s">
-        <v>643</v>
+        <v>56</v>
       </c>
       <c r="R103" s="2">
         <v>4</v>
       </c>
       <c r="S103" s="2" t="s">
-        <v>674</v>
+        <v>556</v>
       </c>
       <c r="T103" s="2" t="str" cm="1">
         <f t="array" ref="T103">_xlfn.REGEXEXTRACT(A103,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubegalore.com</v>
+        <v>pornzog</v>
       </c>
     </row>
     <row r="104" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>784</v>
+        <v>672</v>
       </c>
       <c r="B104" s="2">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>664</v>
+        <v>766</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>785</v>
+        <v>543</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>43</v>
@@ -9359,61 +9342,61 @@
         <v>156</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>123</v>
+        <v>642</v>
       </c>
       <c r="I104" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="J104" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="K104" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="J104" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="K104" s="2" t="s">
+      <c r="L104" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="L104" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="M104" s="2" t="s">
-        <v>638</v>
+        <v>292</v>
       </c>
       <c r="N104" s="2" t="s">
-        <v>152</v>
+        <v>435</v>
       </c>
       <c r="O104" s="2" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="P104" s="2" t="s">
-        <v>43</v>
+        <v>380</v>
       </c>
       <c r="Q104" s="2" t="s">
-        <v>56</v>
+        <v>642</v>
       </c>
       <c r="R104" s="2">
         <v>4</v>
       </c>
       <c r="S104" s="2" t="s">
-        <v>786</v>
+        <v>673</v>
       </c>
       <c r="T104" s="2" t="str" cm="1">
         <f t="array" ref="T104">_xlfn.REGEXEXTRACT(A104,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
+        <v>www.tubegalore.com</v>
       </c>
     </row>
     <row r="105" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="B105" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>789</v>
+        <v>43</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>43</v>
@@ -9422,31 +9405,31 @@
         <v>156</v>
       </c>
       <c r="H105" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="I105" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="I105" s="2" t="s">
-        <v>638</v>
-      </c>
       <c r="J105" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="K105" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="K105" s="2" t="s">
-        <v>137</v>
       </c>
       <c r="L105" s="2" t="s">
         <v>82</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>782</v>
+        <v>637</v>
       </c>
       <c r="N105" s="2" t="s">
-        <v>380</v>
+        <v>152</v>
       </c>
       <c r="O105" s="2" t="s">
-        <v>337</v>
+        <v>91</v>
       </c>
       <c r="P105" s="2" t="s">
-        <v>152</v>
+        <v>43</v>
       </c>
       <c r="Q105" s="2" t="s">
         <v>56</v>
@@ -9455,7 +9438,7 @@
         <v>4</v>
       </c>
       <c r="S105" s="2" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="T105" s="2" t="str" cm="1">
         <f t="array" ref="T105">_xlfn.REGEXEXTRACT(A105,"(?&lt;=//)[^/]+")</f>
@@ -9464,19 +9447,19 @@
     </row>
     <row r="106" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>745</v>
+        <v>786</v>
       </c>
       <c r="B106" s="2">
-        <v>106</v>
+        <v>42</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>685</v>
+        <v>663</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>685</v>
+        <v>787</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>685</v>
+        <v>788</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>43</v>
@@ -9485,121 +9468,121 @@
         <v>156</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>746</v>
+        <v>98</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>747</v>
+        <v>637</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>660</v>
+        <v>60</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>748</v>
+        <v>137</v>
       </c>
       <c r="L106" s="2" t="s">
-        <v>749</v>
+        <v>82</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>651</v>
+        <v>781</v>
       </c>
       <c r="N106" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="O106" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="P106" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="O106" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="P106" s="2" t="s">
-        <v>380</v>
-      </c>
       <c r="Q106" s="2" t="s">
-        <v>643</v>
+        <v>56</v>
       </c>
       <c r="R106" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S106" s="2" t="s">
-        <v>750</v>
+        <v>789</v>
       </c>
       <c r="T106" s="2" t="str" cm="1">
         <f t="array" ref="T106">_xlfn.REGEXEXTRACT(A106,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
+        <v>www.porntry.com</v>
       </c>
     </row>
     <row r="107" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>23</v>
+        <v>744</v>
       </c>
       <c r="B107" s="2">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>224</v>
+        <v>684</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>398</v>
+        <v>684</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>43</v>
+        <v>684</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>103</v>
+        <v>745</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>104</v>
+        <v>746</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>98</v>
+        <v>659</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>106</v>
+        <v>747</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>107</v>
+        <v>748</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>109</v>
+        <v>650</v>
       </c>
       <c r="N107" s="2" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="O107" s="2" t="s">
-        <v>429</v>
+        <v>92</v>
       </c>
       <c r="P107" s="2" t="s">
-        <v>108</v>
+        <v>380</v>
       </c>
       <c r="Q107" s="2" t="s">
-        <v>56</v>
+        <v>642</v>
       </c>
       <c r="R107" s="2">
         <v>3</v>
       </c>
       <c r="S107" s="2" t="s">
-        <v>204</v>
+        <v>749</v>
       </c>
       <c r="T107" s="2" t="str" cm="1">
         <f t="array" ref="T107">_xlfn.REGEXEXTRACT(A107,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>www.eporner.com</v>
       </c>
     </row>
     <row r="108" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>265</v>
+        <v>23</v>
       </c>
       <c r="B108" s="2">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>95</v>
+        <v>224</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>344</v>
+        <v>398</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>43</v>
@@ -9611,31 +9594,31 @@
         <v>80</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>306</v>
+        <v>103</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>520</v>
+        <v>98</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>43</v>
+        <v>107</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>43</v>
+        <v>109</v>
       </c>
       <c r="N108" s="2" t="s">
-        <v>152</v>
+        <v>105</v>
       </c>
       <c r="O108" s="2" t="s">
-        <v>43</v>
+        <v>429</v>
       </c>
       <c r="P108" s="2" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="Q108" s="2" t="s">
         <v>56</v>
@@ -9644,25 +9627,25 @@
         <v>3</v>
       </c>
       <c r="S108" s="2" t="s">
-        <v>499</v>
+        <v>204</v>
       </c>
       <c r="T108" s="2" t="str" cm="1">
         <f t="array" ref="T108">_xlfn.REGEXEXTRACT(A108,"(?&lt;=//)[^/]+")</f>
-        <v>curebdsm.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="109" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>624</v>
+        <v>265</v>
       </c>
       <c r="B109" s="2">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>625</v>
+        <v>344</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>43</v>
@@ -9674,31 +9657,31 @@
         <v>80</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>97</v>
+        <v>306</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>513</v>
+        <v>67</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>626</v>
+        <v>519</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>71</v>
+        <v>98</v>
       </c>
       <c r="L109" s="2" t="s">
-        <v>627</v>
+        <v>43</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="N109" s="2" t="s">
-        <v>112</v>
+        <v>152</v>
       </c>
       <c r="O109" s="2" t="s">
-        <v>628</v>
+        <v>43</v>
       </c>
       <c r="P109" s="2" t="s">
-        <v>629</v>
+        <v>43</v>
       </c>
       <c r="Q109" s="2" t="s">
         <v>56</v>
@@ -9707,61 +9690,61 @@
         <v>3</v>
       </c>
       <c r="S109" s="2" t="s">
-        <v>630</v>
+        <v>498</v>
       </c>
       <c r="T109" s="2" t="str" cm="1">
         <f t="array" ref="T109">_xlfn.REGEXEXTRACT(A109,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>curebdsm.com</v>
       </c>
     </row>
     <row r="110" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>36</v>
+        <v>623</v>
       </c>
       <c r="B110" s="2">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>386</v>
+        <v>111</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>396</v>
+        <v>624</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>402</v>
+        <v>43</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>98</v>
+        <v>512</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>150</v>
+        <v>625</v>
       </c>
       <c r="K110" s="2" t="s">
-        <v>151</v>
+        <v>71</v>
       </c>
       <c r="L110" s="2" t="s">
-        <v>125</v>
+        <v>626</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>153</v>
+        <v>65</v>
       </c>
       <c r="N110" s="2" t="s">
-        <v>68</v>
+        <v>112</v>
       </c>
       <c r="O110" s="2" t="s">
-        <v>152</v>
+        <v>627</v>
       </c>
       <c r="P110" s="2" t="s">
-        <v>43</v>
+        <v>628</v>
       </c>
       <c r="Q110" s="2" t="s">
         <v>56</v>
@@ -9770,7 +9753,7 @@
         <v>3</v>
       </c>
       <c r="S110" s="2" t="s">
-        <v>209</v>
+        <v>629</v>
       </c>
       <c r="T110" s="2" t="str" cm="1">
         <f t="array" ref="T110">_xlfn.REGEXEXTRACT(A110,"(?&lt;=//)[^/]+")</f>
@@ -9779,52 +9762,52 @@
     </row>
     <row r="111" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>480</v>
+        <v>36</v>
       </c>
       <c r="B111" s="2">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>154</v>
+        <v>386</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>481</v>
+        <v>396</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>43</v>
+        <v>402</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>156</v>
+        <v>79</v>
       </c>
       <c r="H111" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="I111" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="I111" s="2" t="s">
-        <v>482</v>
-      </c>
       <c r="J111" s="2" t="s">
-        <v>483</v>
+        <v>150</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>60</v>
+        <v>151</v>
       </c>
       <c r="L111" s="2" t="s">
-        <v>466</v>
+        <v>125</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>484</v>
+        <v>153</v>
       </c>
       <c r="N111" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="O111" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="O111" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="P111" s="2" t="s">
-        <v>380</v>
+        <v>43</v>
       </c>
       <c r="Q111" s="2" t="s">
         <v>56</v>
@@ -9833,25 +9816,25 @@
         <v>3</v>
       </c>
       <c r="S111" s="2" t="s">
-        <v>717</v>
+        <v>209</v>
       </c>
       <c r="T111" s="2" t="str" cm="1">
         <f t="array" ref="T111">_xlfn.REGEXEXTRACT(A111,"(?&lt;=//)[^/]+")</f>
-        <v>pervtube.net</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="112" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>173</v>
+        <v>480</v>
       </c>
       <c r="B112" s="2">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>154</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>174</v>
+        <v>481</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>43</v>
@@ -9863,22 +9846,22 @@
         <v>156</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>175</v>
+        <v>675</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>482</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>176</v>
+        <v>60</v>
       </c>
       <c r="L112" s="2" t="s">
-        <v>60</v>
+        <v>466</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>43</v>
+        <v>483</v>
       </c>
       <c r="N112" s="2" t="s">
         <v>152</v>
@@ -9887,7 +9870,7 @@
         <v>91</v>
       </c>
       <c r="P112" s="2" t="s">
-        <v>43</v>
+        <v>380</v>
       </c>
       <c r="Q112" s="2" t="s">
         <v>56</v>
@@ -9896,25 +9879,25 @@
         <v>3</v>
       </c>
       <c r="S112" s="2" t="s">
-        <v>212</v>
+        <v>716</v>
       </c>
       <c r="T112" s="2" t="str" cm="1">
         <f t="array" ref="T112">_xlfn.REGEXEXTRACT(A112,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
+        <v>pervtube.net</v>
       </c>
     </row>
     <row r="113" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>18</v>
+        <v>173</v>
       </c>
       <c r="B113" s="2">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>273</v>
+        <v>154</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>437</v>
+        <v>174</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>43</v>
@@ -9923,34 +9906,34 @@
         <v>43</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>414</v>
+        <v>82</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>98</v>
+        <v>175</v>
       </c>
       <c r="J113" s="2" t="s">
-        <v>117</v>
+        <v>675</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>116</v>
+        <v>176</v>
       </c>
       <c r="L113" s="2" t="s">
-        <v>549</v>
+        <v>60</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>442</v>
+        <v>43</v>
       </c>
       <c r="N113" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="O113" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="O113" s="2" t="s">
-        <v>190</v>
-      </c>
       <c r="P113" s="2" t="s">
-        <v>149</v>
+        <v>43</v>
       </c>
       <c r="Q113" s="2" t="s">
         <v>56</v>
@@ -9959,61 +9942,61 @@
         <v>3</v>
       </c>
       <c r="S113" s="2" t="s">
-        <v>438</v>
+        <v>212</v>
       </c>
       <c r="T113" s="2" t="str" cm="1">
         <f t="array" ref="T113">_xlfn.REGEXEXTRACT(A113,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.pornhits.com</v>
       </c>
     </row>
     <row r="114" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>716</v>
+        <v>18</v>
       </c>
       <c r="B114" s="2">
         <v>46</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>685</v>
+        <v>273</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>318</v>
+        <v>437</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>450</v>
+        <v>43</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>325</v>
+        <v>80</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>335</v>
+        <v>414</v>
       </c>
       <c r="I114" s="2" t="s">
-        <v>452</v>
+        <v>98</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="K114" s="2" t="s">
-        <v>297</v>
+        <v>116</v>
       </c>
       <c r="L114" s="2" t="s">
-        <v>332</v>
+        <v>548</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="N114" s="2">
-        <v>69</v>
+        <v>442</v>
+      </c>
+      <c r="N114" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="O114" s="2" t="s">
-        <v>91</v>
+        <v>190</v>
       </c>
       <c r="P114" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="Q114" s="2" t="s">
         <v>56</v>
@@ -10022,88 +10005,88 @@
         <v>3</v>
       </c>
       <c r="S114" s="2" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="T114" s="2" t="str" cm="1">
         <f t="array" ref="T114">_xlfn.REGEXEXTRACT(A114,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="115" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>181</v>
+        <v>715</v>
       </c>
       <c r="B115" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>167</v>
+        <v>684</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>183</v>
+        <v>318</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>43</v>
+        <v>450</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>79</v>
+        <v>325</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>67</v>
+        <v>335</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>193</v>
+        <v>452</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="K115" s="2" t="s">
-        <v>196</v>
+        <v>297</v>
       </c>
       <c r="L115" s="2" t="s">
-        <v>43</v>
+        <v>332</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N115" s="2" t="s">
-        <v>194</v>
+        <v>280</v>
+      </c>
+      <c r="N115" s="2">
+        <v>69</v>
       </c>
       <c r="O115" s="2" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="P115" s="2" t="s">
-        <v>43</v>
+        <v>152</v>
       </c>
       <c r="Q115" s="2" t="s">
-        <v>195</v>
+        <v>56</v>
       </c>
       <c r="R115" s="2">
         <v>3</v>
       </c>
       <c r="S115" s="2" t="s">
-        <v>213</v>
+        <v>451</v>
       </c>
       <c r="T115" s="2" t="str" cm="1">
         <f t="array" ref="T115">_xlfn.REGEXEXTRACT(A115,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="116" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>spankbang.com</v>
+      </c>
+    </row>
+    <row r="116" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>258</v>
+        <v>181</v>
       </c>
       <c r="B116" s="2">
         <v>44</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>413</v>
+        <v>167</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>327</v>
+        <v>183</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>43</v>
@@ -10112,19 +10095,19 @@
         <v>43</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>320</v>
+        <v>79</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>414</v>
+        <v>67</v>
       </c>
       <c r="I116" s="2" t="s">
-        <v>84</v>
+        <v>193</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>332</v>
+        <v>137</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>280</v>
+        <v>196</v>
       </c>
       <c r="L116" s="2" t="s">
         <v>43</v>
@@ -10133,40 +10116,40 @@
         <v>43</v>
       </c>
       <c r="N116" s="2" t="s">
-        <v>285</v>
+        <v>194</v>
       </c>
       <c r="O116" s="2" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="P116" s="2" t="s">
-        <v>358</v>
+        <v>43</v>
       </c>
       <c r="Q116" s="2" t="s">
-        <v>56</v>
+        <v>195</v>
       </c>
       <c r="R116" s="2">
         <v>3</v>
       </c>
       <c r="S116" s="2" t="s">
-        <v>415</v>
+        <v>213</v>
       </c>
       <c r="T116" s="2" t="str" cm="1">
         <f t="array" ref="T116">_xlfn.REGEXEXTRACT(A116,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="117" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="117" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>1</v>
+        <v>258</v>
       </c>
       <c r="B117" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>377</v>
+        <v>413</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>131</v>
+        <v>327</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>43</v>
@@ -10178,16 +10161,16 @@
         <v>320</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>297</v>
+        <v>414</v>
       </c>
       <c r="I117" s="2" t="s">
         <v>84</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>83</v>
+        <v>332</v>
       </c>
       <c r="K117" s="2" t="s">
-        <v>332</v>
+        <v>280</v>
       </c>
       <c r="L117" s="2" t="s">
         <v>43</v>
@@ -10196,13 +10179,13 @@
         <v>43</v>
       </c>
       <c r="N117" s="2" t="s">
-        <v>374</v>
+        <v>285</v>
       </c>
       <c r="O117" s="2" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="P117" s="2" t="s">
-        <v>92</v>
+        <v>358</v>
       </c>
       <c r="Q117" s="2" t="s">
         <v>56</v>
@@ -10211,25 +10194,25 @@
         <v>3</v>
       </c>
       <c r="S117" s="2" t="s">
-        <v>378</v>
+        <v>415</v>
       </c>
       <c r="T117" s="2" t="str" cm="1">
         <f t="array" ref="T117">_xlfn.REGEXEXTRACT(A117,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhub.com</v>
-      </c>
-    </row>
-    <row r="118" spans="1:20" ht="30" x14ac:dyDescent="0.25">
+        <v>spankbang.com</v>
+      </c>
+    </row>
+    <row r="118" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>269</v>
+        <v>1</v>
       </c>
       <c r="B118" s="2">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>356</v>
+        <v>131</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>43</v>
@@ -10241,16 +10224,16 @@
         <v>320</v>
       </c>
       <c r="H118" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="I118" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="I118" s="2" t="s">
-        <v>228</v>
-      </c>
       <c r="J118" s="2" t="s">
-        <v>360</v>
+        <v>83</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>125</v>
+        <v>332</v>
       </c>
       <c r="L118" s="2" t="s">
         <v>43</v>
@@ -10259,13 +10242,13 @@
         <v>43</v>
       </c>
       <c r="N118" s="2" t="s">
-        <v>358</v>
+        <v>374</v>
       </c>
       <c r="O118" s="2" t="s">
-        <v>315</v>
+        <v>91</v>
       </c>
       <c r="P118" s="2" t="s">
-        <v>337</v>
+        <v>92</v>
       </c>
       <c r="Q118" s="2" t="s">
         <v>56</v>
@@ -10274,46 +10257,46 @@
         <v>3</v>
       </c>
       <c r="S118" s="2" t="s">
-        <v>359</v>
+        <v>378</v>
       </c>
       <c r="T118" s="2" t="str" cm="1">
         <f t="array" ref="T118">_xlfn.REGEXEXTRACT(A118,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
-      </c>
-    </row>
-    <row r="119" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+        <v>www.pornhub.com</v>
+      </c>
+    </row>
+    <row r="119" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>39</v>
+        <v>269</v>
       </c>
       <c r="B119" s="2">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>189</v>
+        <v>355</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>189</v>
+        <v>356</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>336</v>
+        <v>43</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>81</v>
+        <v>320</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>340</v>
+        <v>84</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>341</v>
+        <v>228</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="K119" s="2" t="s">
-        <v>43</v>
+        <v>125</v>
       </c>
       <c r="L119" s="2" t="s">
         <v>43</v>
@@ -10322,13 +10305,13 @@
         <v>43</v>
       </c>
       <c r="N119" s="2" t="s">
-        <v>152</v>
+        <v>358</v>
       </c>
       <c r="O119" s="2" t="s">
-        <v>159</v>
+        <v>315</v>
       </c>
       <c r="P119" s="2" t="s">
-        <v>43</v>
+        <v>337</v>
       </c>
       <c r="Q119" s="2" t="s">
         <v>56</v>
@@ -10337,61 +10320,61 @@
         <v>3</v>
       </c>
       <c r="S119" s="2" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="T119" s="2" t="str" cm="1">
         <f t="array" ref="T119">_xlfn.REGEXEXTRACT(A119,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>pornxp.com</v>
       </c>
     </row>
     <row r="120" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B120" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>317</v>
+        <v>189</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>318</v>
+        <v>189</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>325</v>
+        <v>81</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>82</v>
+        <v>340</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>83</v>
+        <v>341</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>125</v>
+        <v>343</v>
       </c>
       <c r="K120" s="2" t="s">
-        <v>323</v>
+        <v>43</v>
       </c>
       <c r="L120" s="2" t="s">
-        <v>324</v>
+        <v>43</v>
       </c>
       <c r="M120" s="2" t="s">
         <v>43</v>
       </c>
       <c r="N120" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="O120" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="O120" s="2">
-        <v>69</v>
-      </c>
       <c r="P120" s="2" t="s">
-        <v>101</v>
+        <v>43</v>
       </c>
       <c r="Q120" s="2" t="s">
         <v>56</v>
@@ -10400,61 +10383,61 @@
         <v>3</v>
       </c>
       <c r="S120" s="2" t="s">
-        <v>322</v>
+        <v>342</v>
       </c>
       <c r="T120" s="2" t="str" cm="1">
         <f t="array" ref="T120">_xlfn.REGEXEXTRACT(A120,"(?&lt;=//)[^/]+")</f>
-        <v>tube.perverzija.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="121" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="B121" s="2">
         <v>30</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>43</v>
+        <v>319</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>329</v>
+        <v>83</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>332</v>
+        <v>125</v>
       </c>
       <c r="K121" s="2" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="L121" s="2" t="s">
-        <v>43</v>
+        <v>324</v>
       </c>
       <c r="M121" s="2" t="s">
         <v>43</v>
       </c>
       <c r="N121" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="O121" s="2" t="s">
-        <v>92</v>
+        <v>159</v>
+      </c>
+      <c r="O121" s="2">
+        <v>69</v>
       </c>
       <c r="P121" s="2" t="s">
-        <v>330</v>
+        <v>101</v>
       </c>
       <c r="Q121" s="2" t="s">
         <v>56</v>
@@ -10463,25 +10446,25 @@
         <v>3</v>
       </c>
       <c r="S121" s="2" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="T121" s="2" t="str" cm="1">
         <f t="array" ref="T121">_xlfn.REGEXEXTRACT(A121,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhub.com</v>
+        <v>tube.perverzija.com</v>
       </c>
     </row>
     <row r="122" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="B122" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>131</v>
+        <v>327</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>43</v>
@@ -10490,19 +10473,19 @@
         <v>43</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="I122" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="J122" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="J122" s="2" t="s">
-        <v>280</v>
-      </c>
       <c r="K122" s="2" t="s">
-        <v>43</v>
+        <v>331</v>
       </c>
       <c r="L122" s="2" t="s">
         <v>43</v>
@@ -10511,13 +10494,13 @@
         <v>43</v>
       </c>
       <c r="N122" s="2" t="s">
-        <v>285</v>
+        <v>152</v>
       </c>
       <c r="O122" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P122" s="2" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="Q122" s="2" t="s">
         <v>56</v>
@@ -10526,7 +10509,7 @@
         <v>3</v>
       </c>
       <c r="S122" s="2" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="T122" s="2" t="str" cm="1">
         <f t="array" ref="T122">_xlfn.REGEXEXTRACT(A122,"(?&lt;=//)[^/]+")</f>
@@ -10535,16 +10518,16 @@
     </row>
     <row r="123" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>244</v>
+        <v>2</v>
       </c>
       <c r="B123" s="2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>95</v>
+        <v>314</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>389</v>
+        <v>131</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>43</v>
@@ -10553,34 +10536,34 @@
         <v>43</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>294</v>
+        <v>332</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>98</v>
+        <v>280</v>
       </c>
       <c r="K123" s="2" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="L123" s="2" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="M123" s="2" t="s">
         <v>43</v>
       </c>
       <c r="N123" s="2" t="s">
-        <v>310</v>
+        <v>285</v>
       </c>
       <c r="O123" s="2" t="s">
-        <v>194</v>
+        <v>91</v>
       </c>
       <c r="P123" s="2" t="s">
-        <v>43</v>
+        <v>315</v>
       </c>
       <c r="Q123" s="2" t="s">
         <v>56</v>
@@ -10589,58 +10572,58 @@
         <v>3</v>
       </c>
       <c r="S123" s="2" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="T123" s="2" t="str" cm="1">
         <f t="array" ref="T123">_xlfn.REGEXEXTRACT(A123,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.pornhub.com</v>
       </c>
     </row>
     <row r="124" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>186</v>
+        <v>244</v>
       </c>
       <c r="B124" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>189</v>
+        <v>95</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>187</v>
+        <v>389</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>188</v>
+        <v>43</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>217</v>
+        <v>117</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>218</v>
+        <v>294</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>220</v>
+        <v>98</v>
       </c>
       <c r="K124" s="2" t="s">
-        <v>221</v>
+        <v>71</v>
       </c>
       <c r="L124" s="2" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="M124" s="2" t="s">
         <v>43</v>
       </c>
       <c r="N124" s="2" t="s">
-        <v>216</v>
+        <v>310</v>
       </c>
       <c r="O124" s="2" t="s">
-        <v>43</v>
+        <v>194</v>
       </c>
       <c r="P124" s="2" t="s">
         <v>43</v>
@@ -10652,7 +10635,7 @@
         <v>3</v>
       </c>
       <c r="S124" s="2" t="s">
-        <v>219</v>
+        <v>311</v>
       </c>
       <c r="T124" s="2" t="str" cm="1">
         <f t="array" ref="T124">_xlfn.REGEXEXTRACT(A124,"(?&lt;=//)[^/]+")</f>
@@ -10661,46 +10644,46 @@
     </row>
     <row r="125" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>6</v>
+        <v>186</v>
       </c>
       <c r="B125" s="2">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>301</v>
+        <v>189</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>305</v>
+        <v>187</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>43</v>
+        <v>188</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>117</v>
+        <v>217</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>82</v>
+        <v>218</v>
       </c>
       <c r="J125" s="2" t="s">
-        <v>98</v>
+        <v>220</v>
       </c>
       <c r="K125" s="2" t="s">
-        <v>306</v>
+        <v>221</v>
       </c>
       <c r="L125" s="2" t="s">
-        <v>107</v>
+        <v>43</v>
       </c>
       <c r="M125" s="2" t="s">
         <v>43</v>
       </c>
       <c r="N125" s="2" t="s">
-        <v>90</v>
+        <v>216</v>
       </c>
       <c r="O125" s="2" t="s">
         <v>43</v>
@@ -10715,7 +10698,7 @@
         <v>3</v>
       </c>
       <c r="S125" s="2" t="s">
-        <v>307</v>
+        <v>219</v>
       </c>
       <c r="T125" s="2" t="str" cm="1">
         <f t="array" ref="T125">_xlfn.REGEXEXTRACT(A125,"(?&lt;=//)[^/]+")</f>
@@ -10724,16 +10707,16 @@
     </row>
     <row r="126" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>266</v>
+        <v>6</v>
       </c>
       <c r="B126" s="2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>43</v>
@@ -10742,34 +10725,34 @@
         <v>43</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>332</v>
+        <v>98</v>
       </c>
       <c r="K126" s="2" t="s">
-        <v>228</v>
+        <v>306</v>
       </c>
       <c r="L126" s="2" t="s">
-        <v>287</v>
+        <v>107</v>
       </c>
       <c r="M126" s="2" t="s">
-        <v>288</v>
+        <v>43</v>
       </c>
       <c r="N126" s="2" t="s">
-        <v>285</v>
+        <v>90</v>
       </c>
       <c r="O126" s="2" t="s">
-        <v>91</v>
+        <v>43</v>
       </c>
       <c r="P126" s="2" t="s">
-        <v>286</v>
+        <v>43</v>
       </c>
       <c r="Q126" s="2" t="s">
         <v>56</v>
@@ -10778,25 +10761,25 @@
         <v>3</v>
       </c>
       <c r="S126" s="2" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="T126" s="2" t="str" cm="1">
         <f t="array" ref="T126">_xlfn.REGEXEXTRACT(A126,"(?&lt;=//)[^/]+")</f>
-        <v>www.tnaflix.com</v>
-      </c>
-    </row>
-    <row r="127" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="127" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>24</v>
+        <v>266</v>
       </c>
       <c r="B127" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>74</v>
+        <v>283</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>388</v>
+        <v>284</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>43</v>
@@ -10805,34 +10788,34 @@
         <v>43</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>549</v>
+        <v>66</v>
       </c>
       <c r="I127" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="J127" s="2" t="s">
-        <v>75</v>
+        <v>332</v>
       </c>
       <c r="K127" s="2" t="s">
-        <v>43</v>
+        <v>228</v>
       </c>
       <c r="L127" s="2" t="s">
-        <v>43</v>
+        <v>287</v>
       </c>
       <c r="M127" s="2" t="s">
-        <v>43</v>
+        <v>288</v>
       </c>
       <c r="N127" s="2" t="s">
-        <v>72</v>
+        <v>285</v>
       </c>
       <c r="O127" s="2" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="P127" s="2" t="s">
-        <v>43</v>
+        <v>286</v>
       </c>
       <c r="Q127" s="2" t="s">
         <v>56</v>
@@ -10841,25 +10824,25 @@
         <v>3</v>
       </c>
       <c r="S127" s="2" t="s">
-        <v>77</v>
+        <v>289</v>
       </c>
       <c r="T127" s="2" t="str" cm="1">
         <f t="array" ref="T127">_xlfn.REGEXEXTRACT(A127,"(?&lt;=//)[^/]+")</f>
-        <v>anyporn.com</v>
+        <v>www.tnaflix.com</v>
       </c>
     </row>
     <row r="128" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>741</v>
+        <v>24</v>
       </c>
       <c r="B128" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>685</v>
+        <v>74</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>685</v>
+        <v>388</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>43</v>
@@ -10868,16 +10851,16 @@
         <v>43</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>156</v>
+        <v>80</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>676</v>
+        <v>548</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>742</v>
+        <v>76</v>
       </c>
       <c r="J128" s="2" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="K128" s="2" t="s">
         <v>43</v>
@@ -10889,7 +10872,7 @@
         <v>43</v>
       </c>
       <c r="N128" s="2" t="s">
-        <v>380</v>
+        <v>72</v>
       </c>
       <c r="O128" s="2" t="s">
         <v>43</v>
@@ -10898,31 +10881,31 @@
         <v>43</v>
       </c>
       <c r="Q128" s="2" t="s">
-        <v>743</v>
+        <v>56</v>
       </c>
       <c r="R128" s="2">
         <v>3</v>
       </c>
       <c r="S128" s="2" t="s">
-        <v>744</v>
+        <v>77</v>
       </c>
       <c r="T128" s="2" t="str" cm="1">
         <f t="array" ref="T128">_xlfn.REGEXEXTRACT(A128,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="129" spans="1:20" ht="90" x14ac:dyDescent="0.25">
+        <v>anyporn.com</v>
+      </c>
+    </row>
+    <row r="129" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="B129" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>154</v>
+        <v>684</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>738</v>
+        <v>684</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>43</v>
@@ -10934,13 +10917,13 @@
         <v>156</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>97</v>
+        <v>675</v>
       </c>
       <c r="I129" s="2" t="s">
-        <v>84</v>
+        <v>741</v>
       </c>
       <c r="J129" s="2" t="s">
-        <v>739</v>
+        <v>43</v>
       </c>
       <c r="K129" s="2" t="s">
         <v>43</v>
@@ -10952,7 +10935,7 @@
         <v>43</v>
       </c>
       <c r="N129" s="2" t="s">
-        <v>152</v>
+        <v>380</v>
       </c>
       <c r="O129" s="2" t="s">
         <v>43</v>
@@ -10961,31 +10944,31 @@
         <v>43</v>
       </c>
       <c r="Q129" s="2" t="s">
-        <v>56</v>
+        <v>742</v>
       </c>
       <c r="R129" s="2">
         <v>3</v>
       </c>
       <c r="S129" s="2" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="T129" s="2" t="str" cm="1">
         <f t="array" ref="T129">_xlfn.REGEXEXTRACT(A129,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntopedia.com</v>
-      </c>
-    </row>
-    <row r="130" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="130" spans="1:20" ht="90" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>548</v>
+        <v>736</v>
       </c>
       <c r="B130" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>767</v>
+        <v>154</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>300</v>
+        <v>737</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>43</v>
@@ -10994,34 +10977,34 @@
         <v>43</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>549</v>
+        <v>97</v>
       </c>
       <c r="I130" s="2" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>67</v>
+        <v>738</v>
       </c>
       <c r="K130" s="2" t="s">
-        <v>117</v>
+        <v>43</v>
       </c>
       <c r="L130" s="2" t="s">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="M130" s="2" t="s">
-        <v>546</v>
+        <v>43</v>
       </c>
       <c r="N130" s="2" t="s">
-        <v>337</v>
+        <v>152</v>
       </c>
       <c r="O130" s="2" t="s">
-        <v>435</v>
+        <v>43</v>
       </c>
       <c r="P130" s="2" t="s">
-        <v>380</v>
+        <v>43</v>
       </c>
       <c r="Q130" s="2" t="s">
         <v>56</v>
@@ -11030,25 +11013,25 @@
         <v>3</v>
       </c>
       <c r="S130" s="2" t="s">
-        <v>550</v>
+        <v>739</v>
       </c>
       <c r="T130" s="2" t="str" cm="1">
         <f t="array" ref="T130">_xlfn.REGEXEXTRACT(A130,"(?&lt;=//)[^/]+")</f>
-        <v>curebdsm.com</v>
+        <v>www.porntopedia.com</v>
       </c>
     </row>
     <row r="131" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="B131" s="2">
         <v>0</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>344</v>
+        <v>300</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>43</v>
@@ -11060,31 +11043,31 @@
         <v>80</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="I131" s="2" t="s">
         <v>98</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>137</v>
+        <v>67</v>
       </c>
       <c r="K131" s="2" t="s">
-        <v>552</v>
+        <v>117</v>
       </c>
       <c r="L131" s="2" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="M131" s="2" t="s">
-        <v>65</v>
+        <v>545</v>
       </c>
       <c r="N131" s="2" t="s">
-        <v>152</v>
+        <v>337</v>
       </c>
       <c r="O131" s="2" t="s">
-        <v>494</v>
+        <v>435</v>
       </c>
       <c r="P131" s="2" t="s">
-        <v>68</v>
+        <v>380</v>
       </c>
       <c r="Q131" s="2" t="s">
         <v>56</v>
@@ -11093,25 +11076,25 @@
         <v>3</v>
       </c>
       <c r="S131" s="2" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="T131" s="2" t="str" cm="1">
         <f t="array" ref="T131">_xlfn.REGEXEXTRACT(A131,"(?&lt;=//)[^/]+")</f>
         <v>curebdsm.com</v>
       </c>
     </row>
-    <row r="132" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>569</v>
+        <v>550</v>
       </c>
       <c r="B132" s="2">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>570</v>
+        <v>766</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>571</v>
+        <v>344</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>43</v>
@@ -11120,61 +11103,61 @@
         <v>43</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>320</v>
+        <v>80</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>292</v>
+        <v>548</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>572</v>
+        <v>98</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>573</v>
+        <v>137</v>
       </c>
       <c r="K132" s="2" t="s">
-        <v>125</v>
+        <v>551</v>
       </c>
       <c r="L132" s="2" t="s">
-        <v>228</v>
+        <v>67</v>
       </c>
       <c r="M132" s="2" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="N132" s="2" t="s">
-        <v>72</v>
+        <v>152</v>
       </c>
       <c r="O132" s="2" t="s">
-        <v>330</v>
+        <v>493</v>
       </c>
       <c r="P132" s="2" t="s">
-        <v>574</v>
+        <v>68</v>
       </c>
       <c r="Q132" s="2" t="s">
         <v>56</v>
       </c>
       <c r="R132" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S132" s="2" t="s">
-        <v>575</v>
+        <v>552</v>
       </c>
       <c r="T132" s="2" t="str" cm="1">
         <f t="array" ref="T132">_xlfn.REGEXEXTRACT(A132,"(?&lt;=//)[^/]+")</f>
-        <v>www.peekvids.com</v>
-      </c>
-    </row>
-    <row r="133" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+        <v>curebdsm.com</v>
+      </c>
+    </row>
+    <row r="133" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>524</v>
+        <v>568</v>
       </c>
       <c r="B133" s="2">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>525</v>
+        <v>569</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>526</v>
+        <v>570</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>43</v>
@@ -11183,34 +11166,34 @@
         <v>43</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>80</v>
+        <v>320</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>67</v>
+        <v>292</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>110</v>
+        <v>571</v>
       </c>
       <c r="J133" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="K133" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="L133" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="M133" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="K133" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L133" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="M133" s="2" t="s">
-        <v>228</v>
-      </c>
       <c r="N133" s="2" t="s">
-        <v>380</v>
+        <v>72</v>
       </c>
       <c r="O133" s="2" t="s">
-        <v>358</v>
+        <v>330</v>
       </c>
       <c r="P133" s="2" t="s">
-        <v>519</v>
+        <v>573</v>
       </c>
       <c r="Q133" s="2" t="s">
         <v>56</v>
@@ -11219,61 +11202,61 @@
         <v>2</v>
       </c>
       <c r="S133" s="2" t="s">
-        <v>527</v>
+        <v>574</v>
       </c>
       <c r="T133" s="2" t="str" cm="1">
         <f t="array" ref="T133">_xlfn.REGEXEXTRACT(A133,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.peekvids.com</v>
       </c>
     </row>
     <row r="134" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="B134" s="2">
         <v>57</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>436</v>
+        <v>524</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>397</v>
+        <v>525</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>529</v>
+        <v>43</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>420</v>
+        <v>67</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>306</v>
+        <v>84</v>
       </c>
       <c r="K134" s="2" t="s">
-        <v>226</v>
+        <v>98</v>
       </c>
       <c r="L134" s="2" t="s">
-        <v>43</v>
+        <v>332</v>
       </c>
       <c r="M134" s="2" t="s">
-        <v>43</v>
+        <v>228</v>
       </c>
       <c r="N134" s="2" t="s">
-        <v>530</v>
+        <v>380</v>
       </c>
       <c r="O134" s="2" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="P134" s="2" t="s">
-        <v>91</v>
+        <v>518</v>
       </c>
       <c r="Q134" s="2" t="s">
         <v>56</v>
@@ -11282,28 +11265,28 @@
         <v>2</v>
       </c>
       <c r="S134" s="2" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="T134" s="2" t="str" cm="1">
         <f t="array" ref="T134">_xlfn.REGEXEXTRACT(A134,"(?&lt;=//)[^/]+")</f>
-        <v>www.omg.xxx</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="135" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>247</v>
+        <v>527</v>
       </c>
       <c r="B135" s="2">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>222</v>
+        <v>436</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>458</v>
+        <v>397</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>459</v>
+        <v>528</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>43</v>
@@ -11312,31 +11295,31 @@
         <v>81</v>
       </c>
       <c r="H135" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="I135" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="J135" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="K135" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="I135" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="J135" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="K135" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="L135" s="2" t="s">
-        <v>462</v>
+        <v>43</v>
       </c>
       <c r="M135" s="2" t="s">
-        <v>463</v>
+        <v>43</v>
       </c>
       <c r="N135" s="2" t="s">
-        <v>90</v>
+        <v>529</v>
       </c>
       <c r="O135" s="2" t="s">
-        <v>435</v>
+        <v>337</v>
       </c>
       <c r="P135" s="2" t="s">
-        <v>159</v>
+        <v>91</v>
       </c>
       <c r="Q135" s="2" t="s">
         <v>56</v>
@@ -11345,28 +11328,28 @@
         <v>2</v>
       </c>
       <c r="S135" s="2" t="s">
-        <v>461</v>
+        <v>530</v>
       </c>
       <c r="T135" s="2" t="str" cm="1">
         <f t="array" ref="T135">_xlfn.REGEXEXTRACT(A135,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
+        <v>www.omg.xxx</v>
       </c>
     </row>
     <row r="136" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>32</v>
+        <v>247</v>
       </c>
       <c r="B136" s="2">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>111</v>
+        <v>222</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>177</v>
+        <v>458</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>43</v>
+        <v>459</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>43</v>
@@ -11375,31 +11358,31 @@
         <v>81</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>117</v>
+        <v>226</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>67</v>
+        <v>460</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>423</v>
+        <v>83</v>
       </c>
       <c r="K136" s="2" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="L136" s="2" t="s">
-        <v>424</v>
+        <v>462</v>
       </c>
       <c r="M136" s="2" t="s">
-        <v>425</v>
+        <v>463</v>
       </c>
       <c r="N136" s="2" t="s">
-        <v>337</v>
+        <v>90</v>
       </c>
       <c r="O136" s="2" t="s">
-        <v>330</v>
+        <v>435</v>
       </c>
       <c r="P136" s="2" t="s">
-        <v>424</v>
+        <v>159</v>
       </c>
       <c r="Q136" s="2" t="s">
         <v>56</v>
@@ -11408,25 +11391,25 @@
         <v>2</v>
       </c>
       <c r="S136" s="2" t="s">
-        <v>422</v>
+        <v>461</v>
       </c>
       <c r="T136" s="2" t="str" cm="1">
         <f t="array" ref="T136">_xlfn.REGEXEXTRACT(A136,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="137" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+        <v>m.hqporner.com</v>
+      </c>
+    </row>
+    <row r="137" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>261</v>
+        <v>32</v>
       </c>
       <c r="B137" s="2">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>344</v>
+        <v>177</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>43</v>
@@ -11435,34 +11418,34 @@
         <v>43</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>345</v>
+        <v>67</v>
       </c>
       <c r="J137" s="2" t="s">
-        <v>332</v>
+        <v>423</v>
       </c>
       <c r="K137" s="2" t="s">
-        <v>65</v>
+        <v>147</v>
       </c>
       <c r="L137" s="2" t="s">
-        <v>43</v>
+        <v>424</v>
       </c>
       <c r="M137" s="2" t="s">
-        <v>43</v>
+        <v>425</v>
       </c>
       <c r="N137" s="2" t="s">
-        <v>512</v>
+        <v>337</v>
       </c>
       <c r="O137" s="2" t="s">
-        <v>43</v>
+        <v>330</v>
       </c>
       <c r="P137" s="2" t="s">
-        <v>43</v>
+        <v>424</v>
       </c>
       <c r="Q137" s="2" t="s">
         <v>56</v>
@@ -11471,46 +11454,46 @@
         <v>2</v>
       </c>
       <c r="S137" s="2" t="s">
-        <v>346</v>
+        <v>422</v>
       </c>
       <c r="T137" s="2" t="str" cm="1">
         <f t="array" ref="T137">_xlfn.REGEXEXTRACT(A137,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="138" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="B138" s="2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>189</v>
+        <v>95</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>189</v>
+        <v>344</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>188</v>
+        <v>43</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I138" s="2" t="s">
-        <v>308</v>
+        <v>345</v>
       </c>
       <c r="J138" s="2" t="s">
-        <v>98</v>
+        <v>332</v>
       </c>
       <c r="K138" s="2" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="L138" s="2" t="s">
         <v>43</v>
@@ -11519,7 +11502,7 @@
         <v>43</v>
       </c>
       <c r="N138" s="2" t="s">
-        <v>152</v>
+        <v>511</v>
       </c>
       <c r="O138" s="2" t="s">
         <v>43</v>
@@ -11534,7 +11517,7 @@
         <v>2</v>
       </c>
       <c r="S138" s="2" t="s">
-        <v>309</v>
+        <v>346</v>
       </c>
       <c r="T138" s="2" t="str" cm="1">
         <f t="array" ref="T138">_xlfn.REGEXEXTRACT(A138,"(?&lt;=//)[^/]+")</f>
@@ -11543,34 +11526,34 @@
     </row>
     <row r="139" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>237</v>
+        <v>271</v>
       </c>
       <c r="B139" s="2">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>685</v>
+        <v>189</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>238</v>
+        <v>189</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>239</v>
+        <v>188</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>587</v>
+        <v>97</v>
       </c>
       <c r="I139" s="2" t="s">
-        <v>240</v>
+        <v>308</v>
       </c>
       <c r="J139" s="2" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="K139" s="2" t="s">
         <v>43</v>
@@ -11582,10 +11565,10 @@
         <v>43</v>
       </c>
       <c r="N139" s="2" t="s">
-        <v>241</v>
+        <v>152</v>
       </c>
       <c r="O139" s="2" t="s">
-        <v>152</v>
+        <v>43</v>
       </c>
       <c r="P139" s="2" t="s">
         <v>43</v>
@@ -11597,7 +11580,7 @@
         <v>2</v>
       </c>
       <c r="S139" s="2" t="s">
-        <v>719</v>
+        <v>309</v>
       </c>
       <c r="T139" s="2" t="str" cm="1">
         <f t="array" ref="T139">_xlfn.REGEXEXTRACT(A139,"(?&lt;=//)[^/]+")</f>
@@ -11606,49 +11589,49 @@
     </row>
     <row r="140" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B140" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>230</v>
+        <v>684</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>43</v>
+        <v>239</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>156</v>
+        <v>79</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>232</v>
+        <v>586</v>
       </c>
       <c r="I140" s="2" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="J140" s="2" t="s">
-        <v>234</v>
+        <v>43</v>
       </c>
       <c r="K140" s="2" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="L140" s="2" t="s">
-        <v>235</v>
+        <v>43</v>
       </c>
       <c r="M140" s="2" t="s">
-        <v>236</v>
+        <v>43</v>
       </c>
       <c r="N140" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="O140" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="O140" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="P140" s="2" t="s">
         <v>43</v>
@@ -11667,18 +11650,18 @@
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="141" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>243</v>
+        <v>229</v>
       </c>
       <c r="B141" s="2">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>189</v>
+        <v>230</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>189</v>
+        <v>231</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>43</v>
@@ -11687,31 +11670,31 @@
         <v>43</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>81</v>
+        <v>156</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>446</v>
+        <v>232</v>
       </c>
       <c r="I141" s="2" t="s">
-        <v>43</v>
+        <v>233</v>
       </c>
       <c r="J141" s="2" t="s">
-        <v>43</v>
+        <v>234</v>
       </c>
       <c r="K141" s="2" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="L141" s="2" t="s">
-        <v>43</v>
+        <v>235</v>
       </c>
       <c r="M141" s="2" t="s">
-        <v>43</v>
+        <v>236</v>
       </c>
       <c r="N141" s="2" t="s">
-        <v>216</v>
+        <v>152</v>
       </c>
       <c r="O141" s="2" t="s">
-        <v>152</v>
+        <v>43</v>
       </c>
       <c r="P141" s="2" t="s">
         <v>43</v>
@@ -11720,31 +11703,31 @@
         <v>56</v>
       </c>
       <c r="R141" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S141" s="2" t="s">
-        <v>464</v>
+        <v>717</v>
       </c>
       <c r="T141" s="2" t="str" cm="1">
         <f t="array" ref="T141">_xlfn.REGEXEXTRACT(A141,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="142" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>184</v>
+        <v>243</v>
       </c>
       <c r="B142" s="2">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>189</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>188</v>
+        <v>43</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>43</v>
@@ -11753,16 +11736,16 @@
         <v>81</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>158</v>
+        <v>446</v>
       </c>
       <c r="I142" s="2" t="s">
-        <v>191</v>
+        <v>43</v>
       </c>
       <c r="J142" s="2" t="s">
-        <v>110</v>
+        <v>43</v>
       </c>
       <c r="K142" s="2" t="s">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="L142" s="2" t="s">
         <v>43</v>
@@ -11771,10 +11754,10 @@
         <v>43</v>
       </c>
       <c r="N142" s="2" t="s">
-        <v>190</v>
+        <v>216</v>
       </c>
       <c r="O142" s="2" t="s">
-        <v>43</v>
+        <v>152</v>
       </c>
       <c r="P142" s="2" t="s">
         <v>43</v>
@@ -11786,7 +11769,7 @@
         <v>1</v>
       </c>
       <c r="S142" s="2" t="s">
-        <v>192</v>
+        <v>464</v>
       </c>
       <c r="T142" s="2" t="str" cm="1">
         <f t="array" ref="T142">_xlfn.REGEXEXTRACT(A142,"(?&lt;=//)[^/]+")</f>
@@ -11795,37 +11778,37 @@
     </row>
     <row r="143" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>3</v>
+        <v>184</v>
       </c>
       <c r="B143" s="2">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>296</v>
+        <v>189</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>131</v>
+        <v>187</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>43</v>
+        <v>188</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>43</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>320</v>
+        <v>81</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>292</v>
+        <v>158</v>
       </c>
       <c r="I143" s="2" t="s">
-        <v>293</v>
+        <v>191</v>
       </c>
       <c r="J143" s="2" t="s">
-        <v>294</v>
+        <v>110</v>
       </c>
       <c r="K143" s="2" t="s">
-        <v>297</v>
+        <v>65</v>
       </c>
       <c r="L143" s="2" t="s">
         <v>43</v>
@@ -11834,10 +11817,10 @@
         <v>43</v>
       </c>
       <c r="N143" s="2" t="s">
-        <v>295</v>
+        <v>190</v>
       </c>
       <c r="O143" s="2" t="s">
-        <v>285</v>
+        <v>43</v>
       </c>
       <c r="P143" s="2" t="s">
         <v>43</v>
@@ -11849,25 +11832,25 @@
         <v>1</v>
       </c>
       <c r="S143" s="2" t="s">
-        <v>298</v>
+        <v>192</v>
       </c>
       <c r="T143" s="2" t="str" cm="1">
         <f t="array" ref="T143">_xlfn.REGEXEXTRACT(A143,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhub.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="144" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>795</v>
+        <v>3</v>
       </c>
       <c r="B144" s="2">
-        <v>54</v>
+        <v>11</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>154</v>
+        <v>296</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>796</v>
+        <v>131</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>43</v>
@@ -11876,31 +11859,31 @@
         <v>43</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>156</v>
+        <v>320</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>117</v>
+        <v>292</v>
       </c>
       <c r="I144" s="2" t="s">
-        <v>98</v>
+        <v>293</v>
       </c>
       <c r="J144" s="2" t="s">
-        <v>466</v>
+        <v>294</v>
       </c>
       <c r="K144" s="2" t="s">
-        <v>60</v>
+        <v>297</v>
       </c>
       <c r="L144" s="2" t="s">
-        <v>234</v>
+        <v>43</v>
       </c>
       <c r="M144" s="2" t="s">
-        <v>343</v>
+        <v>43</v>
       </c>
       <c r="N144" s="2" t="s">
-        <v>152</v>
+        <v>295</v>
       </c>
       <c r="O144" s="2" t="s">
-        <v>91</v>
+        <v>285</v>
       </c>
       <c r="P144" s="2" t="s">
         <v>43</v>
@@ -11909,14 +11892,14 @@
         <v>56</v>
       </c>
       <c r="R144" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="S144" s="2" t="s">
-        <v>797</v>
+        <v>298</v>
       </c>
       <c r="T144" s="2" t="str" cm="1">
         <f t="array" ref="T144">_xlfn.REGEXEXTRACT(A144,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
+        <v>www.pornhub.com</v>
       </c>
     </row>
   </sheetData>
